--- a/analysis_visualization/1.2_tools_annotated.xlsx
+++ b/analysis_visualization/1.2_tools_annotated.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2141,6 +2141,2071 @@
         </is>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>ATAE-LSTM</t>
+        </is>
+      </c>
+      <c r="B52">
+        <v>26</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>algorithm</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>ATAE‑LSTM is an attention‑based LSTM architecture designed for aspect‑level sentiment (opinion) analysis. It can be used to measure opinions in text and is specifically built for that purpose, but it is a model architecture rather than a packaged software tool.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>LSA</t>
+        </is>
+      </c>
+      <c r="B53">
+        <v>26</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>algorithm</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Latent Semantic Analysis (LSA) is a statistical algorithm for extracting semantic structure from text. It can be incorporated into opinion/sentiment analysis pipelines, but it is not itself a tool specifically designed for measuring opinions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gradient Boosting</t>
+        </is>
+      </c>
+      <c r="B54">
+        <v>25</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>algorithm</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Gradient Boosting is a general ensemble learning algorithm that can be applied to classification tasks such as sentiment or opinion analysis, but it is not specifically designed for opinion measurement and is not itself a software package.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>IAN</t>
+        </is>
+      </c>
+      <c r="B55">
+        <v>25</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>other_unclear</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>The acronym "IAN" is ambiguous without additional context; it could refer to a variety of tools, frameworks, or resources, and it is not clear whether it pertains to opinion measurement or is provided as installable software.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Bing Liu Opinion Lexicon</t>
+        </is>
+      </c>
+      <c r="B56">
+        <v>24</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>linguistic_resource</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>A lexical resource containing positive and negative opinion words compiled by Bing Liu, used specifically for sentiment and opinion analysis but provided as a data list rather than installable software.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="B57">
+        <v>23</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>programming_language</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>R is a general-purpose programming language and environment for statistical computing; it can be used to implement opinion measurement methods via packages, but the language itself is not a dedicated opinion measurement tool.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>k-means</t>
+        </is>
+      </c>
+      <c r="B58">
+        <v>23</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>algorithm</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>k-means is a general unsupervised clustering algorithm; it is not designed for extracting or measuring opinions from text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>RapidMiner</t>
+        </is>
+      </c>
+      <c r="B59">
+        <v>22</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>gui_tool</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>RapidMiner is a visual data science platform with GUI-based workflows that includes text mining and sentiment analysis operators, allowing it to be used for opinion measurement but it is not dedicated solely to that purpose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>TD-LSTM</t>
+        </is>
+      </c>
+      <c r="B60">
+        <v>22</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>algorithm</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>TD-LSTM (Target‑Dependent LSTM) is a neural network architecture designed for aspect‑based sentiment analysis, enabling opinion measurement focused on specific targets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>doc2vec</t>
+        </is>
+      </c>
+      <c r="B61">
+        <v>22</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>algorithm</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>doc2vec is a general algorithm for learning document embeddings; it can be used as features for opinion/sentiment analysis but is not specifically designed for opinion measurement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Bernoulli Naive Bayes</t>
+        </is>
+      </c>
+      <c r="B62">
+        <v>21</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>algorithm</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Bernoulli Naive Bayes is a probabilistic classification algorithm that can be applied to binary feature vectors, often used for text classification tasks such as sentiment analysis, but it is a general algorithm not specifically built for opinion measurement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>JST</t>
+        </is>
+      </c>
+      <c r="B63">
+        <v>21</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>algorithm</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>JST (Joint Sentiment‑Topic model) is a probabilistic algorithm that jointly models sentiment and topics for opinion mining; it can be used to measure opinions and is specifically designed for that purpose, but its availability as a reusable, installable software package is unclear.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>MPQA</t>
+        </is>
+      </c>
+      <c r="B64">
+        <v>21</v>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>linguistic_resource</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>The MPQA (Multi‑Perspective Question Answering) Opinion Corpus and associated lexicon provide annotated data for subjectivity and opinion detection, specifically designed for opinion measurement but are provided as a dataset rather than installable software.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Keras</t>
+        </is>
+      </c>
+      <c r="B65">
+        <v>20</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>general_library</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Keras is a high‑level deep‑learning library for building neural network models; it can be used to create opinion/sentiment classifiers but is not specifically designed for opinion measurement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>General Inquirer</t>
+        </is>
+      </c>
+      <c r="B66">
+        <v>19</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>linguistic_resource</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>The General Inquirer is a lexical resource that provides sentiment and other semantic categories for words, enabling opinion and sentiment analysis; it is specifically designed for opinion measurement but is a data resource rather than installable software.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>SVC</t>
+        </is>
+      </c>
+      <c r="B67">
+        <v>19</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>algorithm</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Support Vector Classifier (SVC) is a machine‑learning algorithm for classification tasks; it can be employed for sentiment or opinion analysis but is not specifically designed for opinion measurement and is not a standalone software package.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>DBN</t>
+        </is>
+      </c>
+      <c r="B68">
+        <v>18</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>algorithm</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>DBN (Deep Belief Network) is a neural network learning architecture that can be applied to many tasks, including sentiment or opinion analysis, but it is not a dedicated opinion‑measurement tool and is not itself a software package.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Gensim</t>
+        </is>
+      </c>
+      <c r="B69">
+        <v>18</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>general_purpose_nlp</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Gensim is a Python library for topic modeling, word embeddings, and similarity retrieval. It can be leveraged for opinion measurement (e.g., via sentiment‑related embeddings) but is not built specifically for that purpose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>SMOTE</t>
+        </is>
+      </c>
+      <c r="B70">
+        <v>18</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>algorithm</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>SMOTE (Synthetic Minority Over-sampling Technique) is a data‑augmentation algorithm for handling class imbalance; it does not extract or analyze opinions from text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Stanford Parser</t>
+        </is>
+      </c>
+      <c r="B71">
+        <v>18</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>single_purpose_nlp</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Stanford Parser is a dedicated syntactic parsing tool that produces constituency parse trees; it does not directly measure opinions, though its output can be used as a preprocessing step for opinion analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>ABSA</t>
+        </is>
+      </c>
+      <c r="B72">
+        <v>17</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>ABSA (Aspect‑Based Sentiment Analysis) is a high‑level methodology for extracting opinions about specific aspects of a target, thus it is an approach designed for opinion measurement but not a standalone software package.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Apache Spark</t>
+        </is>
+      </c>
+      <c r="B73">
+        <v>17</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>infrastructure</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Apache Spark is an open‑source distributed computing framework for large‑scale data processing. It can be used to run opinion‑measurement pipelines, but it does not itself provide opinion or sentiment analysis functionality.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Genetic Algorithm</t>
+        </is>
+      </c>
+      <c r="B74">
+        <v>16</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>algorithm</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Genetic Algorithm is a general optimization metaheuristic used to search for solutions in various domains; it is not a tool for extracting opinions from text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>J48</t>
+        </is>
+      </c>
+      <c r="B75">
+        <v>16</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>algorithm</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>J48 is the implementation of the C4.5 decision‑tree algorithm (e.g., in WEKA). It is a general classification algorithm that can be applied to opinion/sentiment tasks but is not specifically designed for opinion measurement and is not itself a reusable software package.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>LinearSVC</t>
+        </is>
+      </c>
+      <c r="B76">
+        <v>16</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>algorithm</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>LinearSVC is a linear support‑vector classification algorithm (often from scikit‑learn) that can be applied to sentiment or opinion classification tasks, but it is a general learning method, not a tool built specifically for opinion measurement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Machine Learning</t>
+        </is>
+      </c>
+      <c r="B77">
+        <v>16</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Machine learning is a broad methodological approach for building predictive models, which can be applied to opinion/sentiment analysis but is not itself a software tool nor specifically designed for opinion measurement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Sentiment140</t>
+        </is>
+      </c>
+      <c r="B78">
+        <v>16</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Sentiment140 provides a pre‑trained sentiment classifier (trained on 1.6 M tweets) accessible via an API, designed specifically to detect opinion polarity in short texts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Transformer</t>
+        </is>
+      </c>
+      <c r="B79">
+        <v>16</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>algorithm</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>The Transformer is a general neural network architecture for sequence modeling; it can be employed for opinion/sentiment analysis but is not itself a dedicated opinion measurement tool.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>BiLSTM-CRF</t>
+        </is>
+      </c>
+      <c r="B80">
+        <v>15</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>algorithm</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>BiLSTM-CRF is a neural network architecture (bidirectional LSTM with a CRF layer) used for sequence labeling tasks; it can be trained for opinion‑related tasks such as aspect or opinion target extraction, but it is not itself a dedicated opinion‑measurement tool and is not distributed as a standalone software package.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>MemNet</t>
+        </is>
+      </c>
+      <c r="B81">
+        <v>15</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>algorithm</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>MemNet (Memory Network) is a neural architecture originally proposed for tasks like sentiment analysis; it can be applied to opinion measurement and was designed with sentiment classification in mind, but it is an algorithmic model rather than a packaged software tool.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>OpinionFinder</t>
+        </is>
+      </c>
+      <c r="B82">
+        <v>15</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>single_purpose_nlp</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>OpinionFinder is a dedicated software system specifically designed to detect, extract, and analyze subjective language and opinions expressed in text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Word Embeddings</t>
+        </is>
+      </c>
+      <c r="B83">
+        <v>15</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>other_unclear</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Word embeddings are generic vector representations of words that can be used as features for opinion/sentiment analysis, but they are not a specific software tool, algorithm, or pre‑trained model with a concrete name.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>XLNet</t>
+        </is>
+      </c>
+      <c r="B84">
+        <v>15</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>XLNet is a pre‑trained autoregressive language model that can be fine‑tuned for various NLP tasks, including sentiment or opinion analysis, but it is not specifically built for opinion measurement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>spaCy</t>
+        </is>
+      </c>
+      <c r="B85">
+        <v>15</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>general_purpose_nlp</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>spaCy is a comprehensive Python library for NLP tasks such as tokenization, parsing, and named entity recognition, and can be extended for sentiment or opinion analysis, though it is not built specifically for opinion measurement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>ELMo</t>
+        </is>
+      </c>
+      <c r="B86">
+        <v>14</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>ELMo (Embeddings from Language Models) is a pre‑trained contextual word embedding model that can be fine‑tuned for tasks such as sentiment or opinion analysis, but it was not created specifically for opinion measurement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>PSO</t>
+        </is>
+      </c>
+      <c r="B87">
+        <v>14</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>algorithm</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>PSO (Particle Swarm Optimization) is a general-purpose optimization algorithm; it is not a software tool for extracting opinions and is not specifically designed for opinion measurement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Apache Hadoop MapReduce</t>
+        </is>
+      </c>
+      <c r="B88">
+        <v>13</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>infrastructure</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Apache Hadoop MapReduce is a distributed computing framework for processing large data sets; it can support opinion‑measurement pipelines but is not itself a tool for extracting opinions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>CNN-BiLSTM</t>
+        </is>
+      </c>
+      <c r="B89">
+        <v>13</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>algorithm</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>CNN‑BiLSTM is a neural network architecture combining convolutional layers with a bidirectional LSTM, commonly used for text classification tasks such as sentiment or opinion analysis, but it is a generic algorithm rather than a dedicated opinion‑measurement tool.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Google Cloud Natural Language API</t>
+        </is>
+      </c>
+      <c r="B90">
+        <v>13</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>commercial_api</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Google Cloud Natural Language API is a proprietary cloud service offering NLP functions such as sentiment analysis, entity sentiment, and text classification, enabling extraction of opinions from text; sentiment analysis is a core feature, making it specifically designed for opinion measurement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>NTUSD</t>
+        </is>
+      </c>
+      <c r="B91">
+        <v>13</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>linguistic_resource</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>NTUSD (National Taiwan University Sentiment Dictionary) is a lexical resource providing sentiment scores for Chinese words, designed specifically for sentiment and opinion analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>T5</t>
+        </is>
+      </c>
+      <c r="B92">
+        <v>13</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>T5 (Text‑to‑Text Transfer Transformer) is a pre‑trained transformer model that can be fine‑tuned for many NLP tasks, including sentiment or opinion analysis, but it is not specifically built for opinion measurement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>XLM-RoBERTa</t>
+        </is>
+      </c>
+      <c r="B93">
+        <v>13</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>XLM-RoBERTa is a pre‑trained multilingual transformer model that can be fine‑tuned for various NLP tasks, including sentiment or opinion analysis, but it is not specifically built for opinion measurement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>GCN</t>
+        </is>
+      </c>
+      <c r="B94">
+        <v>12</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>algorithm</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>GCN (Graph Convolutional Network) is a general neural network architecture for learning on graph-structured data; it can be applied to opinion/sentiment tasks but is not specifically built for opinion measurement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>MeaningCloud</t>
+        </is>
+      </c>
+      <c r="B95">
+        <v>12</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>commercial_api</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>MeaningCloud is a commercial cloud‑based API that offers text analytics services such as sentiment and opinion analysis, making it directly usable for measuring opinions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Stanford POS Tagger</t>
+        </is>
+      </c>
+      <c r="B96">
+        <v>12</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>single_purpose_nlp</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>The Stanford POS Tagger is a dedicated tool for part‑of‑speech tagging of text, useful for linguistic preprocessing but not designed to measure opinions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>TC-LSTM</t>
+        </is>
+      </c>
+      <c r="B97">
+        <v>12</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>algorithm</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>TC-LSTM (Target‑Conditioned LSTM) is a neural network architecture designed for aspect‑based sentiment analysis, enabling opinion measurement toward specific targets. It is an algorithmic model rather than a packaged software tool.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>ASUM</t>
+        </is>
+      </c>
+      <c r="B98">
+        <v>11</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>ASUM (Aspect and Sentiment Unification Model) is a pre‑trained probabilistic model for joint aspect extraction and sentiment analysis, specifically designed for opinion measurement, but it is typically described in research papers rather than released as a reusable software package.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>AT-LSTM</t>
+        </is>
+      </c>
+      <c r="B99">
+        <v>11</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>algorithm</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>AT-LSTM is an attention‑based LSTM architecture proposed for aspect‑level sentiment (opinion) analysis; it can be used to measure opinions but is primarily a model design rather than a packaged software tool.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Apache OpenNLP</t>
+        </is>
+      </c>
+      <c r="B100">
+        <v>11</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>general_purpose_nlp</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Apache OpenNLP is an open‑source Java library offering a range of NLP components (tokenizer, POS tagger, NER, etc.) that can be employed to build opinion/sentiment analysis pipelines, though it is not specifically designed for opinion measurement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Attention-BiLSTM</t>
+        </is>
+      </c>
+      <c r="B101">
+        <v>11</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>algorithm</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Attention‑BiLSTM is a neural network architecture (bidirectional LSTM with an attention mechanism) that can be applied to tasks like sentiment or opinion analysis, but it is a general method rather than a dedicated opinion‑measurement tool.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Bayesian Network</t>
+        </is>
+      </c>
+      <c r="B102">
+        <v>11</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>algorithm</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>A probabilistic graphical model used for reasoning under uncertainty; it can be applied to opinion/sentiment classification tasks but is not a tool specifically designed for opinion measurement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>DCNN</t>
+        </is>
+      </c>
+      <c r="B103">
+        <v>11</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>algorithm</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>DCNN (Deep Convolutional Neural Network) is a neural network architecture that can be applied to many text classification tasks, including sentiment or opinion analysis, but it is not itself a dedicated opinion measurement tool.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>DistilBERT</t>
+        </is>
+      </c>
+      <c r="B104">
+        <v>11</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>DistilBERT is a pre‑trained, distilled transformer language model that can be fine‑tuned for tasks such as sentiment or opinion analysis, but it is not specifically built for opinion measurement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Gaussian Naive Bayes</t>
+        </is>
+      </c>
+      <c r="B105">
+        <v>11</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>algorithm</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Gaussian Naive Bayes is a probabilistic classification algorithm that can be applied to sentiment or opinion classification tasks, but it is a general machine‑learning method, not a dedicated opinion‑measurement tool.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>HMM</t>
+        </is>
+      </c>
+      <c r="B106">
+        <v>11</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>algorithm</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Hidden Markov Model (HMM) is a statistical sequence modeling algorithm that can be applied to tasks like sentiment or opinion analysis, but it is a general algorithm not specifically built for opinion measurement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>NVivo</t>
+        </is>
+      </c>
+      <c r="B107">
+        <v>11</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>gui_tool</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>NVivo is a commercial qualitative data analysis desktop application with a graphical user interface that supports coding and analysis of textual data, allowing researchers to examine opinions and sentiments, though it is not specifically built for opinion measurement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>SnowNLP</t>
+        </is>
+      </c>
+      <c r="B108">
+        <v>11</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>general_purpose_nlp</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>SnowNLP is a Python library for Chinese text processing that provides functions such as sentiment analysis, text classification, and keyword extraction; it can be used for opinion measurement but is not dedicated solely to that purpose.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>TensorFlow</t>
+        </is>
+      </c>
+      <c r="B109">
+        <v>11</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>general_library</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>TensorFlow is an open‑source machine learning framework that can be used to build models for many tasks, including opinion/sentiment analysis, but it is not specifically designed for opinion measurement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>n-gram</t>
+        </is>
+      </c>
+      <c r="B110">
+        <v>11</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>approach</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>n‑gram is a textual representation technique (e.g., unigrams, bigrams) used in many NLP models, including sentiment and opinion analysis, but it is a methodological concept rather than a specific software tool.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/analysis_visualization/1.2_tools_annotated.xlsx
+++ b/analysis_visualization/1.2_tools_annotated.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G110"/>
+  <dimension ref="A1:H110"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -372,20 +372,25 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>opinion_measurement_general</t>
+          <t>task_representation</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>opinion_measurement_specific</t>
+          <t>task_classification</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>task_target</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>software</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>note</t>
         </is>
@@ -412,17 +417,22 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Support Vector Machine (SVM) is a general machine‑learning algorithm that can be applied to classification tasks such as sentiment or opinion analysis, but it is not specifically designed for opinion measurement and is not itself a reusable software package.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Support Vector Machine (SVM) is a general machine‑learning algorithm that can be applied to classification tasks such as sentiment or opinion analysis, but it is not specifically designed for opinion measurement and is not provided as standalone software.</t>
         </is>
       </c>
     </row>
@@ -447,17 +457,22 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Naive Bayes is a general probabilistic classification algorithm that can be applied to sentiment or opinion analysis tasks, but it is not specifically designed for opinion measurement.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Naive Bayes is a general probabilistic classification algorithm that can be applied to sentiment or opinion detection tasks, but it is not specifically designed for opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -492,7 +507,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Long Short-Term Memory (LSTM) is a recurrent neural network architecture that can be employed for various tasks, including sentiment or opinion analysis, but it is not a dedicated opinion measurement tool.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Long Short‑Term Memory (LSTM) is a recurrent neural network architecture that can be employed for many sequence tasks, including sentiment or opinion analysis, but it is a general algorithm rather than a tool specifically built for opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -527,7 +547,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>CNN (Convolutional Neural Network) is a deep‑learning model architecture that can be applied to text classification tasks such as sentiment or opinion analysis, but it is a general algorithm rather than a tool specifically built for opinion measurement.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>CNN (Convolutional Neural Network) is a deep‑learning algorithm that can be applied to text classification and sentiment analysis, but it is a general model architecture rather than a tool specifically built for opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -552,17 +577,22 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>BERT is a pre‑trained transformer language model that can be fine‑tuned for various NLP tasks, including sentiment or opinion analysis, but it is not specifically built for opinion measurement.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>BERT is a pre‑trained transformer language model that can be fine‑tuned for many NLP tasks, including sentiment or opinion analysis, but it is not a tool specifically built for opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -587,17 +617,22 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Random Forest is an ensemble learning algorithm that can be applied to classification tasks such as sentiment or opinion analysis, but it is not a tool specifically built for opinion measurement.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Random Forest is a general ensemble learning algorithm for classification and regression. It can be applied to opinion/sentiment classification tasks but is not specifically designed for opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -632,7 +667,12 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SentiWordNet is a lexical resource that assigns sentiment scores to WordNet synsets, enabling sentiment and opinion analysis; it is specifically created for opinion measurement but is provided as a dataset rather than installable software.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>SentiWordNet is a lexical resource that assigns sentiment scores to WordNet synsets, designed specifically for sentiment and opinion analysis, but it is a data resource rather than executable software.</t>
         </is>
       </c>
     </row>
@@ -667,7 +707,12 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>VADER (Valence Aware Dictionary and sEntiment Reasoner) is a rule‑based sentiment analysis tool that provides polarity scores for text, specifically designed for opinion/sentiment measurement and available as a reusable Python library.</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>VADER (Valence Aware Dictionary and sEntiment Reasoner) is a rule‑based sentiment analysis tool that provides polarity scores for text. It is specifically designed for opinion/sentiment measurement and is available as a reusable Python package.</t>
         </is>
       </c>
     </row>
@@ -692,7 +737,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -702,7 +747,12 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Logistic Regression is a general statistical classification algorithm that can be applied to sentiment or opinion detection tasks, but it is not specifically designed for opinion measurement.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Logistic Regression is a general supervised learning algorithm for binary or multiclass classification. It can be applied to opinion/sentiment classification tasks but is not specifically designed for opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -722,7 +772,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -737,7 +787,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>word2vec is a neural embedding algorithm (CBOW/skip‑gram) for learning word vectors; it provides representations that can be used as features in opinion‑measurement models but does not itself extract opinions and is not a packaged software tool.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Word2vec is a word‑embedding learning algorithm that produces vector representations of words; it can be used as a feature source for downstream opinion‑measurement models but does not itself extract or classify opinions.</t>
         </is>
       </c>
     </row>
@@ -757,7 +812,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -772,7 +827,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Latent Dirichlet Allocation (LDA) is a probabilistic topic‑modeling algorithm used to discover latent topics in text corpora; it is not specifically designed for extracting opinions, though topics may sometimes be leveraged for downstream opinion analysis.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Latent Dirichlet Allocation (LDA) is a probabilistic topic‑modeling algorithm. It can be used as a component in opinion‑mining pipelines but is not itself a tool for extracting opinions, nor is it provided as standalone software.</t>
         </is>
       </c>
     </row>
@@ -807,7 +867,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>BiLSTM (Bidirectional LSTM) is a neural network architecture that can be applied to many NLP tasks, including sentiment or opinion analysis, but it is a general algorithm rather than a dedicated opinion‑measurement tool.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>BiLSTM (Bidirectional Long Short‑Term Memory) is a neural network architecture used for sequence modeling. It can be applied to opinion/sentiment analysis but is a general algorithm, not a dedicated opinion measurement tool.</t>
         </is>
       </c>
     </row>
@@ -842,7 +907,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Decision Tree is a general machine‑learning algorithm for classification and regression that can be applied to sentiment or opinion analysis tasks, but it is not specifically designed for opinion measurement.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Decision Tree is a general machine‑learning algorithm for classification and regression that can be applied to opinion/sentiment analysis but is not specifically designed for that purpose.</t>
         </is>
       </c>
     </row>
@@ -877,7 +947,12 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>TextBlob is a Python library that provides easy‑to‑use APIs for various NLP tasks, including sentiment analysis, making it usable for opinion measurement but not dedicated solely to that purpose.</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>TextBlob is a Python library offering simple APIs for common NLP tasks, including sentiment analysis, making it usable for opinion measurement but not dedicated solely to that purpose.</t>
         </is>
       </c>
     </row>
@@ -912,7 +987,12 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>RNN (Recurrent Neural Network) is a general neural network architecture that can be applied to tasks like sentiment or opinion analysis, but it is not itself a software package nor specifically designed for opinion measurement.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>RNN (Recurrent Neural Network) is a general neural network architecture that can be applied to many sequence tasks, including sentiment or opinion analysis, but it is not a tool specifically built for opinion measurement and is not provided as standalone software.</t>
         </is>
       </c>
     </row>
@@ -947,7 +1027,12 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>TF‑IDF is a term‑weighting algorithm used to represent text as vectors; it can be employed as features for sentiment or opinion classification but is not itself a dedicated opinion‑measurement tool.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>TF‑IDF is a term‑weighting algorithm used to represent text as vectors; it can be employed as a feature extraction step for opinion‑related classifiers but is not itself a tool specifically built for opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -972,7 +1057,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -982,7 +1067,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>GloVe provides pre‑trained word embedding vectors that can be used as features for various NLP tasks, including sentiment or opinion analysis, but it is not a tool specifically designed for opinion measurement.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>GloVe provides pre‑trained word‑embedding vectors that can be used as features for opinion/sentiment analysis, but it is not a tool specifically built for opinion measurement and the resource itself is data rather than installable software.</t>
         </is>
       </c>
     </row>
@@ -1017,7 +1107,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>NLTK is a comprehensive Python library for NLP tasks such as tokenization, POS tagging, and sentiment analysis. It can be used for opinion measurement but is not specifically designed for it.</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>NLTK is a comprehensive Python library for many NLP tasks, including tokenization, POS tagging, and sentiment analysis. It can be used for opinion measurement but is not specifically built for that purpose.</t>
         </is>
       </c>
     </row>
@@ -1042,17 +1137,22 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>K-Nearest Neighbors (KNN) is a general classification algorithm that can be applied to sentiment or opinion analysis tasks, but it is not specifically designed for opinion measurement.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>K‑Nearest Neighbors (KNN) is a general‑purpose classification algorithm that can be applied to sentiment or opinion analysis tasks, but it is not specifically designed for opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1187,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>GRU (Gated Recurrent Unit) is a recurrent neural network architecture that can be employed in models for sentiment or opinion analysis, but it is a general algorithm not specifically built for opinion measurement.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>GRU (Gated Recurrent Unit) is a recurrent neural network architecture that can be employed in models for sentiment or opinion analysis, but it is a general algorithm rather than a tool specifically built for opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1227,12 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SentiStrength is a Java‑based tool that estimates the strength of positive and negative sentiment in short informal texts, designed specifically for opinion/sentiment measurement.</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>SentiStrength is a dedicated Java‑based tool that estimates the strength of positive and negative sentiment in short informal texts, making it directly usable for opinion measurement and specifically designed for that purpose.</t>
         </is>
       </c>
     </row>
@@ -1157,7 +1267,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Multinomial Naive Bayes is a probabilistic classification algorithm commonly applied to text classification tasks such as sentiment analysis, enabling opinion measurement but not designed exclusively for it.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Multinomial Naive Bayes is a general probabilistic classification algorithm often applied to text classification tasks, including sentiment analysis, but it is not a software package and is not specifically designed for opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -1182,7 +1297,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1192,7 +1307,12 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Stanford CoreNLP is a comprehensive Java library offering a suite of NLP tools, including tokenization, parsing, and sentiment analysis, which can be used for opinion measurement but is not solely dedicated to it.</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Stanford CoreNLP is a comprehensive Java-based NLP library offering tokenization, parsing, POS‑tagging, and a sentiment analysis component, making it usable for opinion measurement but not dedicated solely to that purpose.</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1347,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Conditional Random Fields (CRF) are a general sequence‑labeling algorithm that can be applied to opinion‑related tasks such as aspect extraction or sentiment tagging, but they are not specifically built for opinion measurement.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Conditional Random Field (CRF) is a general sequence‑labeling algorithm that can be applied to opinion‑related tasks such as aspect extraction or sentiment tagging, but it is not specifically designed for opinion measurement and is not itself a software package.</t>
         </is>
       </c>
     </row>
@@ -1252,17 +1377,22 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Maximum Entropy (also known as the MaxEnt classifier) is a general-purpose statistical classification algorithm that can be applied to sentiment or opinion analysis but is not specifically designed for that purpose.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Maximum Entropy (also known as the MaxEnt classifier or logistic regression) is a general-purpose statistical learning algorithm that can be applied to classification tasks such as sentiment or opinion analysis, but it is not specifically designed for opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -1297,7 +1427,12 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>ANN (Artificial Neural Network) is a general machine‑learning algorithm/architecture that can be applied to sentiment or opinion analysis tasks, but it is not specifically designed for opinion measurement and is not itself a reusable software package.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Artificial Neural Network (ANN) is a general machine‑learning algorithm that can be applied to many tasks, including sentiment or opinion analysis, but it is not specifically designed for opinion measurement and is not itself a reusable software package.</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1447,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>single_purpose_nlp</t>
+          <t>general_purpose_nlp</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1322,7 +1457,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1332,7 +1467,12 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>fastText is an open‑source library for learning word embeddings and performing fast text classification; it can be applied to sentiment or opinion analysis but is not specifically built for opinion measurement.</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>fastText is an open‑source library for learning word embeddings and performing fast text classification. It can be applied to opinion/sentiment analysis but is not built specifically for that purpose.</t>
         </is>
       </c>
     </row>
@@ -1347,7 +1487,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>gui_tool</t>
+          <t>single_purpose_nlp</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1357,7 +1497,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1367,7 +1507,12 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>LIWC (Linguistic Inquiry and Word Count) is a proprietary GUI‑based software that provides psycholinguistic word‑count categories, including affective dimensions, and can be used to infer opinions or sentiment, though it is not built specifically for opinion measurement.</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>LIWC (Linguistic Inquiry and Word Count) is a proprietary software tool that uses a psycholinguistic dictionary to quantify affective and cognitive dimensions in text, enabling both general and specifically designed opinion/sentiment measurement.</t>
         </is>
       </c>
     </row>
@@ -1397,10 +1542,15 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
         <is>
           <t>Tweepy is a Python library that provides an interface to the Twitter API for collecting tweets and other Twitter data. It does not perform opinion measurement itself.</t>
         </is>
@@ -1417,7 +1567,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>general_library</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1437,7 +1587,12 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>XGBoost is a general‑purpose machine‑learning library implementing gradient‑boosted decision trees. It can be applied to opinion/sentiment classification tasks but is not designed specifically for opinion measurement.</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>XGBoost is a gradient‑boosted decision tree algorithm with an open‑source library implementation. It can be applied to opinion/sentiment classification tasks but is not designed specifically for opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1617,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1472,7 +1627,12 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>RoBERTa is a pre‑trained transformer language model that can be fine‑tuned for tasks such as sentiment or opinion analysis, but it was not created specifically for opinion measurement.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>RoBERTa is a pre‑trained transformer language model that can be fine‑tuned for many NLP tasks, including sentiment or opinion analysis, but it is not specifically built for opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -1507,7 +1667,12 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>MLP (Multi-Layer Perceptron) is a general neural network architecture that can be applied to many classification tasks, including sentiment or opinion analysis, but it is not specifically designed for opinion measurement.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>MLP (Multi‑Layer Perceptron) is a general neural‑network learning algorithm that can be applied to many classification problems, including sentiment or opinion analysis, but it is not specifically built for opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1707,12 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>An API for collecting data from Twitter. It enables gathering textual data but does not perform opinion measurement itself.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>The Twitter API is an interface for collecting tweets and other data from the Twitter platform. It enables data gathering but does not itself perform opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -1567,7 +1737,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1577,7 +1747,12 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>WEKA is a Java‑based suite offering a GUI and command‑line interface for applying a wide range of machine‑learning algorithms; it can be used to build opinion/sentiment classifiers but is not designed specifically for opinion measurement.</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>WEKA is a GUI‑based suite of machine learning algorithms for data mining; it can be employed to build opinion/sentiment classifiers but is not specifically designed for opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1782,17 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SenticNet is a concept-level sentiment lexicon that provides affective scores for terms and concepts, designed specifically for sentiment and opinion analysis but provided as a data resource rather than installable software.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>SenticNet is a concept‑level sentiment knowledge base that provides affective scores for terms and multi‑word expressions. It is specifically created for sentiment/opinion analysis, but it is a lexical resource rather than installable software.</t>
         </is>
       </c>
     </row>
@@ -1632,7 +1812,7 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
@@ -1647,7 +1827,12 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>WordNet is a lexical database of English words and their semantic relations. It can be leveraged in opinion measurement pipelines (e.g., for term expansion) but is not specifically designed for sentiment or opinion analysis.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>WordNet is a lexical database that provides semantic relationships between words; it is not specifically designed for opinion measurement and is not software itself.</t>
         </is>
       </c>
     </row>
@@ -1672,17 +1857,22 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>CNN‑LSTM is a hybrid neural network architecture that combines convolutional layers with LSTM units; it can be applied to sentiment or opinion analysis tasks but is not a tool specifically built for opinion measurement.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>CNN‑LSTM is a hybrid neural network architecture that combines convolutional layers with LSTM units. It can be applied to sentiment or opinion analysis but is a generic model design rather than a dedicated opinion‑measurement tool.</t>
         </is>
       </c>
     </row>
@@ -1717,7 +1907,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>AFINN is a lexical resource that provides sentiment scores for English words, designed specifically for sentiment and opinion analysis, but it is a data resource rather than installable software.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>AFINN is a sentiment lexicon that assigns polarity scores to English words, designed specifically for sentiment and opinion analysis, but it is a data resource rather than installable software.</t>
         </is>
       </c>
     </row>
@@ -1747,12 +1942,17 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sentiment analysis is a high‑level methodology for detecting and quantifying affective opinions in text; it is specifically aimed at opinion measurement but is not itself a software package.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Sentiment analysis is a high‑level methodological approach for detecting and quantifying evaluative attitudes in text, used broadly for opinion measurement but not a specific software package.</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1977,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1787,7 +1987,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>scikit-learn is a general‑purpose Python machine‑learning library offering algorithms and tools that can be applied to opinion/sentiment classification, though it is not built specifically for opinion measurement.</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>scikit-learn is a general‑purpose Python machine‑learning library that provides algorithms and utilities for classification, regression, and clustering. It can be employed to build opinion‑measurement models but is not specifically designed for that purpose.</t>
         </is>
       </c>
     </row>
@@ -1822,7 +2027,12 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>The NRC Emotion Lexicon provides word‑level emotion scores (e.g., joy, anger). It can be used to infer affective opinions from text, and it was created specifically for emotion/sentiment analysis, though it is a data resource rather than installable software.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>The NRC Emotion Lexicon is a lexical resource that maps words to emotion categories (e.g., joy, anger). It can be used to infer affective opinions from text, making it applicable for opinion measurement, and it was created specifically for detecting emotions/feelings, a form of opinion measurement. It is not provided as installable software.</t>
         </is>
       </c>
     </row>
@@ -1842,7 +2052,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -1852,12 +2062,17 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Python is a general-purpose programming language and runtime environment; it is not itself used for opinion measurement, though it can be used to implement such tools.</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Python is a general‑purpose programming language and runtime environment; it is not itself used for opinion measurement, but it can be used to implement such tools.</t>
         </is>
       </c>
     </row>
@@ -1882,7 +2097,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1892,7 +2107,12 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>BiGRU (Bidirectional Gated Recurrent Unit) is a neural network architecture that can be employed for various text classification tasks, including sentiment or opinion analysis, but it is not a tool specifically built for opinion measurement.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>BiGRU (Bidirectional Gated Recurrent Unit) is a neural network architecture that can be employed for sentiment or opinion analysis but is a general algorithm, not a dedicated opinion‑measurement tool.</t>
         </is>
       </c>
     </row>
@@ -1922,12 +2142,17 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>A high‑level methodology that uses sentiment lexicons to compute polarity scores for text, directly targeting opinion/sentiment detection.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Lexicon‑based sentiment analysis is a high‑level methodology that uses sentiment lexicons to detect and quantify opinions in text; it is specifically intended for opinion measurement but is not a concrete software package.</t>
         </is>
       </c>
     </row>
@@ -1957,12 +2182,17 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Apache Hadoop is an open‑source distributed computing framework for storing and processing large datasets; it serves as infrastructure rather than a tool that directly extracts opinions.</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Apache Hadoop is an open‑source distributed computing framework for storing and processing large‑scale data. It provides the infrastructure for big‑data pipelines but does not itself perform opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2227,12 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Stochastic Gradient Descent (SGD) is an optimization algorithm used to train machine‑learning models, including those for sentiment or opinion analysis, but it is not itself a tool specifically designed for opinion measurement.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Stochastic Gradient Descent (SGD) is a general optimization algorithm used to train machine‑learning models, including those for sentiment or opinion analysis, but it is not itself a tool specifically designed for opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -2032,7 +2267,12 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>AdaBoost is a general ensemble learning algorithm that can be applied to classification tasks such as sentiment or opinion analysis, but it is not specifically designed for opinion measurement.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>AdaBoost is a general ensemble learning algorithm that can be applied to classification problems, including sentiment or opinion detection, but it is not specifically designed for opinion measurement and is not itself a software package.</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2307,12 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Bag-of-Words is a general text representation approach that can be used as features for opinion/sentiment classification, but it is not a dedicated opinion measurement tool nor provided as installable software.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Bag‑of‑Words is a general text representation approach that can be used as features for opinion/sentiment classification, but it is not a dedicated opinion‑measurement tool nor provided as installable software.</t>
         </is>
       </c>
     </row>
@@ -2102,7 +2347,12 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>DNN (Deep Neural Network) is a general machine‑learning architecture that can be trained for tasks such as sentiment or opinion analysis, but it is not itself a dedicated opinion‑measurement tool.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>DNN (Deep Neural Network) is a general machine‑learning architecture that can be applied to many tasks, including sentiment or opinion analysis, but it is not a specific tool or software designed solely for opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -2137,7 +2387,12 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Deep Learning is a high‑level methodology for building neural network models; it can be applied to opinion/sentiment analysis but is not itself a software tool nor specifically designed for opinion measurement.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Deep Learning is a high‑level methodological approach for building neural network models; it can be applied to opinion measurement but is not itself a specific opinion‑measurement tool.</t>
         </is>
       </c>
     </row>
@@ -2167,12 +2422,17 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>ATAE‑LSTM is an attention‑based LSTM architecture designed for aspect‑level sentiment (opinion) analysis. It can be used to measure opinions in text and is specifically built for that purpose, but it is a model architecture rather than a packaged software tool.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>ATAE‑LSTM is an attention‑based LSTM architecture for aspect‑based sentiment analysis, i.e., a model architecture that can be used to extract opinions from text but is not distributed as a ready‑to‑install software package.</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2452,7 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2207,7 +2467,12 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Latent Semantic Analysis (LSA) is a statistical algorithm for extracting semantic structure from text. It can be incorporated into opinion/sentiment analysis pipelines, but it is not itself a tool specifically designed for measuring opinions.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Latent Semantic Analysis (LSA) is a statistical algorithm for extracting and representing the underlying semantic structure of text. It can be incorporated into opinion‑measurement pipelines but is not specifically designed for that purpose.</t>
         </is>
       </c>
     </row>
@@ -2232,7 +2497,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2242,7 +2507,12 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Gradient Boosting is a general ensemble learning algorithm that can be applied to classification tasks such as sentiment or opinion analysis, but it is not specifically designed for opinion measurement and is not itself a software package.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Gradient Boosting is a general ensemble learning algorithm that can be applied to classification tasks such as sentiment or opinion analysis, but it is not specifically designed for opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2547,12 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>The acronym "IAN" is ambiguous without additional context; it could refer to a variety of tools, frameworks, or resources, and it is not clear whether it pertains to opinion measurement or is provided as installable software.</t>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>The term "IAN" lacks sufficient context to determine its nature (e.g., tool, algorithm, resource) or its applicability to opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -2312,7 +2587,12 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>A lexical resource containing positive and negative opinion words compiled by Bing Liu, used specifically for sentiment and opinion analysis but provided as a data list rather than installable software.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>The Bing Liu Opinion Lexicon is a curated list of positive and negative opinion words used for sentiment and opinion analysis. It is a lexical resource specifically designed for opinion measurement, not a software package.</t>
         </is>
       </c>
     </row>
@@ -2342,12 +2622,17 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>R is a general-purpose programming language and environment for statistical computing; it can be used to implement opinion measurement methods via packages, but the language itself is not a dedicated opinion measurement tool.</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>R is a general-purpose programming language and environment for statistical computing. It can be used to implement opinion measurement methods via packages, but the language itself is not a tool specifically designed for opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2667,12 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>k-means is a general unsupervised clustering algorithm; it is not designed for extracting or measuring opinions from text.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>k-means is a general clustering algorithm used for grouping data points; it is not specifically designed for opinion measurement and is not provided as standalone software.</t>
         </is>
       </c>
     </row>
@@ -2417,7 +2707,12 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>RapidMiner is a visual data science platform with GUI-based workflows that includes text mining and sentiment analysis operators, allowing it to be used for opinion measurement but it is not dedicated solely to that purpose.</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>RapidMiner is a visual data science platform that provides a GUI for building and executing machine‑learning pipelines, including sentiment or opinion analysis via extensions. It can be used for opinion measurement but is not purpose‑built for it.</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2747,12 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>TD-LSTM (Target‑Dependent LSTM) is a neural network architecture designed for aspect‑based sentiment analysis, enabling opinion measurement focused on specific targets.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>TD‑LSTM (Target‑Dependent LSTM) is a neural network architecture proposed for target‑specific sentiment analysis. It can be applied to opinion measurement in general and was specifically designed for that purpose, but it is described as an algorithmic model rather than a released software package.</t>
         </is>
       </c>
     </row>
@@ -2487,7 +2787,12 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>doc2vec is a general algorithm for learning document embeddings; it can be used as features for opinion/sentiment analysis but is not specifically designed for opinion measurement.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>doc2vec (Paragraph Vector) is a general algorithm for learning fixed‑length vector representations of documents. It can be used as features for opinion/sentiment classification, but it is not specifically designed for opinion measurement and is not itself a reusable software package.</t>
         </is>
       </c>
     </row>
@@ -2512,7 +2817,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2522,7 +2827,12 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Bernoulli Naive Bayes is a probabilistic classification algorithm that can be applied to binary feature vectors, often used for text classification tasks such as sentiment analysis, but it is a general algorithm not specifically built for opinion measurement.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Bernoulli Naive Bayes is a probabilistic classification algorithm that can be applied to binary feature vectors, often used for text classification tasks such as sentiment analysis, but it is not specifically designed for opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2867,12 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>JST (Joint Sentiment‑Topic model) is a probabilistic algorithm that jointly models sentiment and topics for opinion mining; it can be used to measure opinions and is specifically designed for that purpose, but its availability as a reusable, installable software package is unclear.</t>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>JST (Joint Sentiment‑Topic) is a probabilistic model that jointly discovers topics and sentiment in text, specifically designed for opinion measurement, but it is primarily a modeling approach rather than a packaged software tool.</t>
         </is>
       </c>
     </row>
@@ -2587,12 +2902,17 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>The MPQA (Multi‑Perspective Question Answering) Opinion Corpus and associated lexicon provide annotated data for subjectivity and opinion detection, specifically designed for opinion measurement but are provided as a dataset rather than installable software.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>MPQA (Multi‑Perspective Question Answering) includes a subjectivity lexicon and opinion corpus designed for detecting subjective expressions and sentiment. It is a lexical/resource asset, not a software package, but it is specifically created for opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2947,12 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Keras is a high‑level deep‑learning library for building neural network models; it can be used to create opinion/sentiment classifiers but is not specifically designed for opinion measurement.</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Keras is a high‑level deep‑learning library for building neural network models. It can be used to create opinion‑measurement models (e.g., sentiment classifiers) but is not itself a dedicated opinion‑measurement tool.</t>
         </is>
       </c>
     </row>
@@ -2657,12 +2982,17 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>The General Inquirer is a lexical resource that provides sentiment and other semantic categories for words, enabling opinion and sentiment analysis; it is specifically designed for opinion measurement but is a data resource rather than installable software.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>The General Inquirer is a lexical resource that provides word categories, including positive/negative sentiment, and is used for opinion and sentiment analysis, but it is a data resource rather than installable software.</t>
         </is>
       </c>
     </row>
@@ -2697,7 +3027,12 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Support Vector Classifier (SVC) is a machine‑learning algorithm for classification tasks; it can be employed for sentiment or opinion analysis but is not specifically designed for opinion measurement and is not a standalone software package.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>SVC (Support Vector Classifier) is a machine‑learning algorithm for binary/multi‑class classification that can be applied to sentiment or opinion detection, but it is not a tool specifically built for opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -2732,7 +3067,12 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>DBN (Deep Belief Network) is a neural network learning architecture that can be applied to many tasks, including sentiment or opinion analysis, but it is not a dedicated opinion‑measurement tool and is not itself a software package.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>DBN (Deep Belief Network) is a general neural network learning algorithm that can be applied to various classification tasks, including sentiment or opinion analysis, but it is not specifically designed for opinion measurement and is not provided as a standalone software package.</t>
         </is>
       </c>
     </row>
@@ -2762,12 +3102,17 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Gensim is a Python library for topic modeling, word embeddings, and similarity retrieval. It can be leveraged for opinion measurement (e.g., via sentiment‑related embeddings) but is not built specifically for that purpose.</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Gensim is a Python library for topic modeling, word embeddings, and similarity analysis. It can be used as a component in opinion‑measurement pipelines but is not itself designed for extracting opinions.</t>
         </is>
       </c>
     </row>
@@ -2802,7 +3147,12 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>SMOTE (Synthetic Minority Over-sampling Technique) is a data‑augmentation algorithm for handling class imbalance; it does not extract or analyze opinions from text.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>SMOTE (Synthetic Minority Over-sampling Technique) is a data‑augmentation algorithm for handling class imbalance. It is not designed to extract or measure opinions from text, nor is it provided as a standalone software package.</t>
         </is>
       </c>
     </row>
@@ -2832,12 +3182,17 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Stanford Parser is a dedicated syntactic parsing tool that produces constituency parse trees; it does not directly measure opinions, though its output can be used as a preprocessing step for opinion analysis.</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Stanford Parser is a dedicated syntactic parsing tool that produces constituency parse trees. It can be used as a component in opinion‑analysis pipelines but is not itself designed for measuring opinions.</t>
         </is>
       </c>
     </row>
@@ -2872,7 +3227,12 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>ABSA (Aspect‑Based Sentiment Analysis) is a high‑level methodology for extracting opinions about specific aspects of a target, thus it is an approach designed for opinion measurement but not a standalone software package.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>ABSA (Aspect‑Based Sentiment Analysis) is a high‑level methodology for extracting opinions about specific aspects of a target, making it a general and specifically designed opinion measurement approach, but it is not a standalone software package.</t>
         </is>
       </c>
     </row>
@@ -2907,7 +3267,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Apache Spark is an open‑source distributed computing framework for large‑scale data processing. It can be used to run opinion‑measurement pipelines, but it does not itself provide opinion or sentiment analysis functionality.</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Apache Spark is an open‑source distributed computing framework for large‑scale data processing. It does not itself perform opinion measurement, though it can be used as a platform to run sentiment‑analysis pipelines.</t>
         </is>
       </c>
     </row>
@@ -2927,7 +3292,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -2942,7 +3307,12 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Genetic Algorithm is a general optimization metaheuristic used to search for solutions in various domains; it is not a tool for extracting opinions from text.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Genetic Algorithm is a general-purpose optimization metaheuristic that can be applied to various problems, including training classifiers for sentiment or opinion analysis, but it is not specifically designed for opinion measurement and is not itself a software package.</t>
         </is>
       </c>
     </row>
@@ -2977,7 +3347,12 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>J48 is the implementation of the C4.5 decision‑tree algorithm (e.g., in WEKA). It is a general classification algorithm that can be applied to opinion/sentiment tasks but is not specifically designed for opinion measurement and is not itself a reusable software package.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>J48 is an implementation of the C4.5 decision‑tree algorithm (commonly used in WEKA). It is a general classification algorithm that can be applied to opinion/sentiment tasks but is not specifically designed for opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -3012,7 +3387,12 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>LinearSVC is a linear support‑vector classification algorithm (often from scikit‑learn) that can be applied to sentiment or opinion classification tasks, but it is a general learning method, not a tool built specifically for opinion measurement.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>LinearSVC is a linear Support Vector Classification algorithm (often accessed via scikit‑learn). It can be applied to sentiment or opinion classification tasks but is not specifically built for opinion measurement and is not a standalone software package.</t>
         </is>
       </c>
     </row>
@@ -3047,7 +3427,12 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Machine learning is a broad methodological approach for building predictive models, which can be applied to opinion/sentiment analysis but is not itself a software tool nor specifically designed for opinion measurement.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Machine learning is a broad methodological approach for building predictive models, which can be applied to opinion measurement tasks but is not itself a software tool nor specifically designed for opinion analysis.</t>
         </is>
       </c>
     </row>
@@ -3062,27 +3447,32 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>linguistic_resource</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Sentiment140 provides a pre‑trained sentiment classifier (trained on 1.6 M tweets) accessible via an API, designed specifically to detect opinion polarity in short texts.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Sentiment140 is a corpus of 1.6 million tweets annotated with sentiment labels, used as a resource for training/evaluating sentiment analysis models rather than as a software tool.</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3497,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3117,7 +3507,12 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>The Transformer is a general neural network architecture for sequence modeling; it can be employed for opinion/sentiment analysis but is not itself a dedicated opinion measurement tool.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>The Transformer is a neural network architecture (algorithm) that underlies many modern NLP models. It can be employed for opinion measurement when fine‑tuned, but it is not itself a tool specifically designed for that purpose and is not provided as standalone software.</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3547,12 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>BiLSTM-CRF is a neural network architecture (bidirectional LSTM with a CRF layer) used for sequence labeling tasks; it can be trained for opinion‑related tasks such as aspect or opinion target extraction, but it is not itself a dedicated opinion‑measurement tool and is not distributed as a standalone software package.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>BiLSTM‑CRF is a neural network architecture (bidirectional LSTM with a CRF layer) used for sequence labeling; it can be trained for opinion‑related tasks (e.g., aspect extraction) but is not itself a dedicated opinion‑measurement tool and is not a packaged software.</t>
         </is>
       </c>
     </row>
@@ -3167,7 +3567,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>model</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3182,12 +3582,17 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>MemNet (Memory Network) is a neural architecture originally proposed for tasks like sentiment analysis; it can be applied to opinion measurement and was designed with sentiment classification in mind, but it is an algorithmic model rather than a packaged software tool.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>MemNet (Memory Network) is a deep neural model introduced for sentiment analysis; it can be used to infer opinions from text and was specifically designed for that purpose, but it is a pre‑trained model rather than a standalone installable software package.</t>
         </is>
       </c>
     </row>
@@ -3222,7 +3627,12 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>OpinionFinder is a dedicated software system specifically designed to detect, extract, and analyze subjective language and opinions expressed in text.</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>OpinionFinder is a dedicated software system specifically designed to detect and analyze subjective language and opinions in text.</t>
         </is>
       </c>
     </row>
@@ -3237,7 +3647,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>other_unclear</t>
+          <t>model</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3257,7 +3667,12 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Word embeddings are generic vector representations of words that can be used as features for opinion/sentiment analysis, but they are not a specific software tool, algorithm, or pre‑trained model with a concrete name.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Word embeddings are pre‑trained vector representations of words (e.g., Word2Vec, GloVe). They can be used as features for opinion measurement but are not specifically designed for that purpose and are not software themselves.</t>
         </is>
       </c>
     </row>
@@ -3282,15 +3697,20 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
         <is>
           <t>XLNet is a pre‑trained autoregressive language model that can be fine‑tuned for various NLP tasks, including sentiment or opinion analysis, but it is not specifically built for opinion measurement.</t>
         </is>
@@ -3327,7 +3747,12 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>spaCy is a comprehensive Python library for NLP tasks such as tokenization, parsing, and named entity recognition, and can be extended for sentiment or opinion analysis, though it is not built specifically for opinion measurement.</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>spaCy is a comprehensive Python library for NLP tasks such as tokenization, parsing, and named entity recognition, and it can be extended for opinion/sentiment analysis, though it is not built specifically for that purpose.</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3782,17 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>ELMo (Embeddings from Language Models) is a pre‑trained contextual word embedding model that can be fine‑tuned for tasks such as sentiment or opinion analysis, but it was not created specifically for opinion measurement.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>ELMo (Embeddings from Language Models) is a pre‑trained contextual word‑embedding model that can be used as features for sentiment or opinion analysis, but it is not specifically built for opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -3382,7 +3812,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3397,7 +3827,12 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>PSO (Particle Swarm Optimization) is a general-purpose optimization algorithm; it is not a software tool for extracting opinions and is not specifically designed for opinion measurement.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Particle Swarm Optimization (PSO) is a general meta‑heuristic optimization algorithm. It can be used to train models for many tasks, including sentiment analysis, but it is not itself a tool for extracting opinions from text and is not specifically designed for opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -3427,12 +3862,17 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Apache Hadoop MapReduce is a distributed computing framework for processing large data sets; it can support opinion‑measurement pipelines but is not itself a tool for extracting opinions.</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Apache Hadoop MapReduce is a distributed computing framework for processing large data sets. It is not itself an opinion measurement tool, though it can be used to run opinion analysis pipelines.</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3907,12 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>CNN‑BiLSTM is a neural network architecture combining convolutional layers with a bidirectional LSTM, commonly used for text classification tasks such as sentiment or opinion analysis, but it is a generic algorithm rather than a dedicated opinion‑measurement tool.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>CNN‑BiLSTM is a neural network architecture that combines convolutional layers with a bidirectional LSTM. It can be applied to opinion/sentiment analysis but is not itself a dedicated opinion‑measurement tool, nor is it a packaged software component.</t>
         </is>
       </c>
     </row>
@@ -3502,7 +3947,12 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Google Cloud Natural Language API is a proprietary cloud service offering NLP functions such as sentiment analysis, entity sentiment, and text classification, enabling extraction of opinions from text; sentiment analysis is a core feature, making it specifically designed for opinion measurement.</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Google Cloud Natural Language API is a cloud‑based commercial service that provides NLP functions including sentiment analysis, enabling general and specific opinion measurement via an API.</t>
         </is>
       </c>
     </row>
@@ -3537,7 +3987,12 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>NTUSD (National Taiwan University Sentiment Dictionary) is a lexical resource providing sentiment scores for Chinese words, designed specifically for sentiment and opinion analysis.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>NTUSD (National Taiwan University Sentiment Dictionary) is a Chinese sentiment lexicon that provides polarity scores for words, designed specifically for sentiment and opinion analysis but distributed as a data resource rather than installable software.</t>
         </is>
       </c>
     </row>
@@ -3562,17 +4017,22 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>T5 (Text‑to‑Text Transfer Transformer) is a pre‑trained transformer model that can be fine‑tuned for many NLP tasks, including sentiment or opinion analysis, but it is not specifically built for opinion measurement.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>T5 (Text‑to‑Text Transfer Transformer) is a pre‑trained language model that can be fine‑tuned for many downstream tasks, including sentiment or opinion analysis, but it is not built specifically for opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -3597,17 +4057,22 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>XLM-RoBERTa is a pre‑trained multilingual transformer model that can be fine‑tuned for various NLP tasks, including sentiment or opinion analysis, but it is not specifically built for opinion measurement.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>XLM‑RoBERTa is a pre‑trained multilingual transformer model that can be fine‑tuned for various NLP tasks, including sentiment or opinion analysis, but it is not specifically built for opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -3632,17 +4097,22 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>GCN (Graph Convolutional Network) is a general neural network architecture for learning on graph-structured data; it can be applied to opinion/sentiment tasks but is not specifically built for opinion measurement.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>GCN (Graph Convolutional Network) is a general neural network architecture for learning on graph-structured data. It can be applied to opinion/sentiment analysis tasks but is not specifically built for opinion measurement, and it is an algorithm rather than a standalone software package.</t>
         </is>
       </c>
     </row>
@@ -3677,6 +4147,11 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
           <t>MeaningCloud is a commercial cloud‑based API that offers text analytics services such as sentiment and opinion analysis, making it directly usable for measuring opinions.</t>
         </is>
       </c>
@@ -3697,7 +4172,7 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3707,12 +4182,17 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>The Stanford POS Tagger is a dedicated tool for part‑of‑speech tagging of text, useful for linguistic preprocessing but not designed to measure opinions.</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>The Stanford POS Tagger is a dedicated tool for part‑of‑speech tagging of text. It is software that can be installed and run, but it is not designed for opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -3742,12 +4222,17 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>TC-LSTM (Target‑Conditioned LSTM) is a neural network architecture designed for aspect‑based sentiment analysis, enabling opinion measurement toward specific targets. It is an algorithmic model rather than a packaged software tool.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>TC‑LSTM (Target‑Conditioned LSTM) is a neural network architecture designed for target‑dependent sentiment (opinion) analysis. It can be used for general opinion measurement and is specifically built for that purpose, but it is an algorithmic description rather than a packaged, installable software tool.</t>
         </is>
       </c>
     </row>
@@ -3777,12 +4262,17 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>ASUM (Aspect and Sentiment Unification Model) is a pre‑trained probabilistic model for joint aspect extraction and sentiment analysis, specifically designed for opinion measurement, but it is typically described in research papers rather than released as a reusable software package.</t>
+          <t>unclear</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>ASUM (Aspect and Sentiment Unification Model) is a probabilistic model designed for joint aspect extraction and sentiment analysis, i.e., opinion measurement. It can be used for opinion measurement in general and is specifically built for that purpose, though it is unclear whether a reusable, installable software package is publicly available.</t>
         </is>
       </c>
     </row>
@@ -3817,7 +4307,12 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>AT-LSTM is an attention‑based LSTM architecture proposed for aspect‑level sentiment (opinion) analysis; it can be used to measure opinions but is primarily a model design rather than a packaged software tool.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>AT-LSTM is an attention‑based LSTM architecture proposed for aspect‑level sentiment (opinion) analysis. It can be used to measure opinions in text and is specifically designed for that purpose, but it is described as a model architecture rather than a packaged, installable software tool.</t>
         </is>
       </c>
     </row>
@@ -3852,7 +4347,12 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Apache OpenNLP is an open‑source Java library offering a range of NLP components (tokenizer, POS tagger, NER, etc.) that can be employed to build opinion/sentiment analysis pipelines, though it is not specifically designed for opinion measurement.</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Apache OpenNLP is an open‑source Java library offering a range of NLP components (tokenizer, POS tagger, NER, parser, etc.). It can be employed for opinion/sentiment analysis but is not built specifically for that purpose.</t>
         </is>
       </c>
     </row>
@@ -3887,7 +4387,12 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Attention‑BiLSTM is a neural network architecture (bidirectional LSTM with an attention mechanism) that can be applied to tasks like sentiment or opinion analysis, but it is a general method rather than a dedicated opinion‑measurement tool.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Attention‑BiLSTM is a neural network architecture (bidirectional LSTM with an attention mechanism) that can be applied to many text classification tasks, including sentiment or opinion analysis, but it is not a ready‑to‑use software package nor specifically built for opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -3922,7 +4427,12 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>A probabilistic graphical model used for reasoning under uncertainty; it can be applied to opinion/sentiment classification tasks but is not a tool specifically designed for opinion measurement.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>A Bayesian Network is a probabilistic graphical model used for reasoning under uncertainty; it can be applied to opinion measurement tasks but is a general algorithmic framework, not a dedicated opinion‑measurement tool, and it is not itself a software package.</t>
         </is>
       </c>
     </row>
@@ -3957,7 +4467,12 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>DCNN (Deep Convolutional Neural Network) is a neural network architecture that can be applied to many text classification tasks, including sentiment or opinion analysis, but it is not itself a dedicated opinion measurement tool.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>DCNN (Deep Convolutional Neural Network) is a neural network architecture that can be applied to many text classification tasks, including sentiment or opinion analysis, but it is not a tool specifically designed for opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -3982,17 +4497,22 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>DistilBERT is a pre‑trained, distilled transformer language model that can be fine‑tuned for tasks such as sentiment or opinion analysis, but it is not specifically built for opinion measurement.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>DistilBERT is a pre‑trained, distilled transformer model derived from BERT. It can be fine‑tuned for sentiment or opinion analysis, but it is a generic language model rather than a tool built specifically for opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -4017,17 +4537,22 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Gaussian Naive Bayes is a probabilistic classification algorithm that can be applied to sentiment or opinion classification tasks, but it is a general machine‑learning method, not a dedicated opinion‑measurement tool.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Gaussian Naive Bayes is a probabilistic classification algorithm that can be applied to sentiment or opinion classification tasks, but it is a general machine‑learning method rather than a tool specifically built for opinion measurement.</t>
         </is>
       </c>
     </row>
@@ -4052,17 +4577,22 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Hidden Markov Model (HMM) is a statistical sequence modeling algorithm that can be applied to tasks like sentiment or opinion analysis, but it is a general algorithm not specifically built for opinion measurement.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Hidden Markov Model (HMM) is a statistical algorithm for modeling sequential data. It can be applied to opinion/sentiment analysis tasks but is not specifically designed for opinion measurement and is not provided as standalone software.</t>
         </is>
       </c>
     </row>
@@ -4097,7 +4627,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>NVivo is a commercial qualitative data analysis desktop application with a graphical user interface that supports coding and analysis of textual data, allowing researchers to examine opinions and sentiments, though it is not specifically built for opinion measurement.</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>NVivo is a commercial desktop application with a graphical user interface for qualitative data analysis. It can be used to code and explore opinionated text, but it is not a dedicated opinion‑measurement system.</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4667,12 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>SnowNLP is a Python library for Chinese text processing that provides functions such as sentiment analysis, text classification, and keyword extraction; it can be used for opinion measurement but is not dedicated solely to that purpose.</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>SnowNLP is a Python library for Chinese text processing that provides functions for sentiment analysis, text classification, keyword extraction, etc. It can be used for opinion measurement but is not dedicated solely to that purpose.</t>
         </is>
       </c>
     </row>
@@ -4157,7 +4697,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4167,7 +4707,12 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>TensorFlow is an open‑source machine learning framework that can be used to build models for many tasks, including opinion/sentiment analysis, but it is not specifically designed for opinion measurement.</t>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>TensorFlow is a widely‑used open‑source deep‑learning framework that can be employed to build models for opinion/sentiment analysis, though it is not specifically designed for that purpose.</t>
         </is>
       </c>
     </row>
@@ -4202,7 +4747,12 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>n‑gram is a textual representation technique (e.g., unigrams, bigrams) used in many NLP models, including sentiment and opinion analysis, but it is a methodological concept rather than a specific software tool.</t>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>An n‑gram is a statistical language modeling approach that captures contiguous sequences of tokens; it can be used as a feature for opinion/sentiment analysis but is not a dedicated opinion measurement tool.</t>
         </is>
       </c>
     </row>

--- a/analysis_visualization/1.2_tools_annotated.xlsx
+++ b/analysis_visualization/1.2_tools_annotated.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H110"/>
+  <dimension ref="A1:H118"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -399,20 +399,20 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SVM</t>
+          <t>ABSA</t>
         </is>
       </c>
       <c r="B2">
-        <v>646</v>
+        <v>17</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>approach</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -432,27 +432,27 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Support Vector Machine (SVM) is a general machine‑learning algorithm that can be applied to classification tasks such as sentiment or opinion analysis, but it is not specifically designed for opinion measurement and is not provided as standalone software.</t>
+          <t>Aspect-Based Sentiment Analysis (ABSA) is a high-level NLP approach that jointly identifies specific aspects or targets in text and classifies the sentiment or opinion directed toward them. It is a conceptual framework and research task rather than a specific installable software product.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Naive Bayes</t>
+          <t>AFINN</t>
         </is>
       </c>
       <c r="B3">
-        <v>531</v>
+        <v>39</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>linguistic_resource</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -462,28 +462,28 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Naive Bayes is a general probabilistic classification algorithm that can be applied to sentiment or opinion detection tasks, but it is not specifically designed for opinion measurement.</t>
+          <t>AFINN is a widely used opinion lexicon that assigns valence scores to words. It is distributed as installable Python and R packages for lexicon-based sentiment analysis.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>LSTM</t>
+          <t>ANN</t>
         </is>
       </c>
       <c r="B4">
-        <v>352</v>
+        <v>64</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -497,7 +497,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -512,37 +512,37 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Long Short‑Term Memory (LSTM) is a recurrent neural network architecture that can be employed for many sequence tasks, including sentiment or opinion analysis, but it is a general algorithm rather than a tool specifically built for opinion measurement.</t>
+          <t>ANN (Artificial Neural Network) is a general machine learning architecture used as a foundational algorithm for learning numerical text representations and performing classification tasks. It is not a specific software product or a tool exclusively designed for opinion measurement.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CNN</t>
+          <t>ASUM</t>
         </is>
       </c>
       <c r="B5">
-        <v>327</v>
+        <v>11</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>model</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -552,27 +552,27 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>CNN (Convolutional Neural Network) is a deep‑learning algorithm that can be applied to text classification and sentiment analysis, but it is a general model architecture rather than a tool specifically built for opinion measurement.</t>
+          <t>ASUM (Aspect Sentiment Unification Model) is a research architecture designed for aspect-based sentiment analysis, jointly identifying opinion targets and classifying their sentiment polarity. It is primarily a neural model proposed in academic literature rather than a standalone installable software package.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BERT</t>
+          <t>AT-LSTM</t>
         </is>
       </c>
       <c r="B6">
-        <v>295</v>
+        <v>11</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -592,18 +592,18 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>BERT is a pre‑trained transformer language model that can be fine‑tuned for many NLP tasks, including sentiment or opinion analysis, but it is not a tool specifically built for opinion measurement.</t>
+          <t>AT-LSTM (Attention-based Long Short-Term Memory) is a neural network architecture that combines sequential LSTM processing with an attention mechanism. It is primarily used as a classification algorithm for tasks like sentiment analysis and text classification, but it is a conceptual model architecture rather than a standalone software product.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Random Forest</t>
+          <t>ATAE-LSTM</t>
         </is>
       </c>
       <c r="B7">
-        <v>260</v>
+        <v>26</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -612,7 +612,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -632,27 +632,27 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Random Forest is a general ensemble learning algorithm for classification and regression. It can be applied to opinion/sentiment classification tasks but is not specifically designed for opinion measurement.</t>
+          <t>ATAE-LSTM is a deep learning architecture specifically designed for aspect-based sentiment analysis, jointly performing aspect term extraction and sentiment classification. It is a research model architecture rather than a packaged software product.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SentiWordNet</t>
+          <t>AdaBoost</t>
         </is>
       </c>
       <c r="B8">
-        <v>211</v>
+        <v>28</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>linguistic_resource</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -672,37 +672,37 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>SentiWordNet is a lexical resource that assigns sentiment scores to WordNet synsets, designed specifically for sentiment and opinion analysis, but it is a data resource rather than executable software.</t>
+          <t>AdaBoost (Adaptive Boosting) is a general machine learning ensemble algorithm primarily used for classification tasks. It combines multiple weak learners to improve predictive accuracy but is not specifically designed for opinion measurement or text processing.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>VADER</t>
+          <t>Apache Hadoop</t>
         </is>
       </c>
       <c r="B9">
-        <v>198</v>
+        <v>31</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>single_purpose_nlp</t>
+          <t>infrastructure</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -712,32 +712,32 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>VADER (Valence Aware Dictionary and sEntiment Reasoner) is a rule‑based sentiment analysis tool that provides polarity scores for text. It is specifically designed for opinion/sentiment measurement and is available as a reusable Python package.</t>
+          <t>Apache Hadoop is a distributed computing framework designed for storing and processing large datasets across clusters of computers. While it provides the computational infrastructure for scaling NLP pipelines, it does not perform text analysis or opinion measurement itself.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Logistic Regression</t>
+          <t>Apache Hadoop MapReduce</t>
         </is>
       </c>
       <c r="B10">
-        <v>196</v>
+        <v>13</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>infrastructure</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -747,27 +747,27 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Logistic Regression is a general supervised learning algorithm for binary or multiclass classification. It can be applied to opinion/sentiment classification tasks but is not specifically designed for opinion measurement.</t>
+          <t>Apache Hadoop MapReduce is a distributed computing framework used for processing large-scale data across clusters. It provides the computational infrastructure for running NLP pipelines at scale but does not perform text analysis or opinion measurement itself.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>word2vec</t>
+          <t>Apache OpenNLP</t>
         </is>
       </c>
       <c r="B11">
-        <v>189</v>
+        <v>11</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>general_purpose_nlp</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -777,42 +777,42 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Word2vec is a word‑embedding learning algorithm that produces vector representations of words; it can be used as a feature source for downstream opinion‑measurement models but does not itself extract or classify opinions.</t>
+          <t>Apache OpenNLP is a general-purpose Java library for natural language processing that provides components for tokenization, POS tagging, chunking, and named entity recognition. It can be used to build opinion measurement pipelines but is not specifically designed solely for opinion analysis.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>LDA</t>
+          <t>Apache Spark</t>
         </is>
       </c>
       <c r="B12">
-        <v>167</v>
+        <v>17</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>infrastructure</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -827,27 +827,27 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Latent Dirichlet Allocation (LDA) is a probabilistic topic‑modeling algorithm. It can be used as a component in opinion‑mining pipelines but is not itself a tool for extracting opinions, nor is it provided as standalone software.</t>
+          <t>A distributed computing framework for large-scale data processing. It provides the infrastructure for running NLP pipelines at scale but performs no text analysis itself.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BiLSTM</t>
+          <t>AraBERT</t>
         </is>
       </c>
       <c r="B13">
-        <v>148</v>
+        <v>10</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>model</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -872,18 +872,18 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>BiLSTM (Bidirectional Long Short‑Term Memory) is a neural network architecture used for sequence modeling. It can be applied to opinion/sentiment analysis but is a general algorithm, not a dedicated opinion measurement tool.</t>
+          <t>AraBERT is a pre-trained Arabic transformer language model developed for general NLP tasks. It provides contextual text representations and can be fine-tuned for classification tasks, but is not specifically designed for opinion measurement.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Decision Tree</t>
+          <t>Attention-BiLSTM</t>
         </is>
       </c>
       <c r="B14">
-        <v>135</v>
+        <v>11</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -892,12 +892,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -912,22 +912,22 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Decision Tree is a general machine‑learning algorithm for classification and regression that can be applied to opinion/sentiment analysis but is not specifically designed for that purpose.</t>
+          <t>Attention-BiLSTM is a neural network architecture that combines bidirectional recurrent networks with an attention mechanism, primarily used for sequence modeling and text classification tasks such as sentiment or stance analysis. It is a conceptual model architecture rather than a standalone software package.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>TextBlob</t>
+          <t>BERT</t>
         </is>
       </c>
       <c r="B15">
-        <v>134</v>
+        <v>295</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>general_purpose_nlp</t>
+          <t>model</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -937,37 +937,37 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>TextBlob is a Python library offering simple APIs for common NLP tasks, including sentiment analysis, making it usable for opinion measurement but not dedicated solely to that purpose.</t>
+          <t>BERT is a pre-trained transformer language model that generates contextualized text representations and can be fine-tuned for various NLP tasks, including sentiment and stance analysis, but it is not specifically designed for opinion measurement.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>RNN</t>
+          <t>Bag-of-Words</t>
         </is>
       </c>
       <c r="B16">
-        <v>118</v>
+        <v>28</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>approach</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -992,18 +992,18 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>RNN (Recurrent Neural Network) is a general neural network architecture that can be applied to many sequence tasks, including sentiment or opinion analysis, but it is not a tool specifically built for opinion measurement and is not provided as standalone software.</t>
+          <t>Bag-of-Words is a conceptual text representation method that converts text into numerical vectors by counting word frequencies while ignoring word order. It is a foundational methodology rather than a standalone software product.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TF-IDF</t>
+          <t>Bayesian Network</t>
         </is>
       </c>
       <c r="B17">
-        <v>113</v>
+        <v>11</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>TF‑IDF is a term‑weighting algorithm used to represent text as vectors; it can be employed as a feature extraction step for opinion‑related classifiers but is not itself a tool specifically built for opinion measurement.</t>
+          <t>Bayesian Network is a probabilistic graphical model used for reasoning and classification under uncertainty. It is a general machine learning algorithm rather than a specific software product or opinion measurement tool.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GloVe</t>
+          <t>Bernoulli Naive Bayes</t>
         </is>
       </c>
       <c r="B18">
-        <v>103</v>
+        <v>21</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1072,58 +1072,58 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>GloVe provides pre‑trained word‑embedding vectors that can be used as features for opinion/sentiment analysis, but it is not a tool specifically built for opinion measurement and the resource itself is data rather than installable software.</t>
+          <t>Bernoulli Naive Bayes is a probabilistic classification algorithm that operates on binary feature vectors, commonly applied to text classification tasks like sentiment or stance analysis. It is a mathematical method rather than a standalone software product.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NLTK</t>
+          <t>BiGRU</t>
         </is>
       </c>
       <c r="B19">
-        <v>101</v>
+        <v>32</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>general_purpose_nlp</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>NLTK is a comprehensive Python library for many NLP tasks, including tokenization, POS tagging, and sentiment analysis. It can be used for opinion measurement but is not specifically built for that purpose.</t>
+          <t>Bidirectional Gated Recurrent Unit is a neural network architecture used for sequence modeling. It is commonly employed as a classification backbone in opinion measurement but is not a specific software product or dedicated solely to text representation or target identification.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KNN</t>
+          <t>BiLSTM</t>
         </is>
       </c>
       <c r="B20">
-        <v>93</v>
+        <v>148</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1142,7 +1142,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1152,18 +1152,18 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>K‑Nearest Neighbors (KNN) is a general‑purpose classification algorithm that can be applied to sentiment or opinion analysis tasks, but it is not specifically designed for opinion measurement.</t>
+          <t>Bidirectional Long Short-Term Memory is a neural network architecture used as a general-purpose backbone for sequence modeling and classification tasks, including sentiment and opinion analysis, but it is not a standalone software product or specifically designed for opinion measurement.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GRU</t>
+          <t>BiLSTM-CRF</t>
         </is>
       </c>
       <c r="B21">
-        <v>78</v>
+        <v>15</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -1172,17 +1172,17 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1192,27 +1192,27 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>GRU (Gated Recurrent Unit) is a recurrent neural network architecture that can be employed in models for sentiment or opinion analysis, but it is a general algorithm rather than a tool specifically built for opinion measurement.</t>
+          <t>BiLSTM-CRF is a sequence labeling architecture that combines bidirectional recurrent networks with a conditional random field layer. It is primarily used for token-level classification and target/entity extraction tasks like named entity recognition or aspect term extraction, rather than being a standalone software package.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SentiStrength</t>
+          <t>Bing Liu Opinion Lexicon</t>
         </is>
       </c>
       <c r="B22">
-        <v>78</v>
+        <v>24</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>single_purpose_nlp</t>
+          <t>linguistic_resource</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1222,28 +1222,28 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>SentiStrength is a dedicated Java‑based tool that estimates the strength of positive and negative sentiment in short informal texts, making it directly usable for opinion measurement and specifically designed for that purpose.</t>
+          <t>The Bing Liu Opinion Lexicon is a widely used collection of positive and negative words and phrases specifically curated for sentiment analysis and opinion mining. It serves as a foundational linguistic resource rather than executable software.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Multinomial Naive Bayes</t>
+          <t>CNN</t>
         </is>
       </c>
       <c r="B23">
-        <v>76</v>
+        <v>327</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Multinomial Naive Bayes is a general probabilistic classification algorithm often applied to text classification tasks, including sentiment analysis, but it is not a software package and is not specifically designed for opinion measurement.</t>
+          <t>CNN (Convolutional Neural Network) is a deep learning architecture originally designed for image processing but widely adapted for text classification and feature extraction. It is a general algorithmic framework rather than a specific software product or opinion measurement tool.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Stanford CoreNLP</t>
+          <t>CNN-BiLSTM</t>
         </is>
       </c>
       <c r="B24">
-        <v>70</v>
+        <v>13</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>general_purpose_nlp</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1302,28 +1302,28 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Stanford CoreNLP is a comprehensive Java-based NLP library offering tokenization, parsing, POS‑tagging, and a sentiment analysis component, making it usable for opinion measurement but not dedicated solely to that purpose.</t>
+          <t>A hybrid neural network architecture combining convolutional and bidirectional recurrent layers for sequence modeling. It is widely used for text classification and feature extraction but is a general algorithmic framework rather than a packaged software product.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>CRF</t>
+          <t>CNN-LSTM</t>
         </is>
       </c>
       <c r="B25">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -1332,12 +1332,12 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1352,14 +1352,14 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Conditional Random Field (CRF) is a general sequence‑labeling algorithm that can be applied to opinion‑related tasks such as aspect extraction or sentiment tagging, but it is not specifically designed for opinion measurement and is not itself a software package.</t>
+          <t>CNN-LSTM is a hybrid neural network architecture that combines convolutional and recurrent layers for sequence modeling. It is primarily used for text classification tasks like sentiment analysis, but it is a conceptual model architecture rather than a specific software product or pre-trained model.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Maximum Entropy</t>
+          <t>CRF</t>
         </is>
       </c>
       <c r="B26">
@@ -1372,7 +1372,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1392,18 +1392,18 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Maximum Entropy (also known as the MaxEnt classifier or logistic regression) is a general-purpose statistical learning algorithm that can be applied to classification tasks such as sentiment or opinion analysis, but it is not specifically designed for opinion measurement.</t>
+          <t>Conditional Random Fields (CRF) is a statistical sequence labeling algorithm widely used in NLP for tasks like named entity recognition and aspect extraction. It is a mathematical modeling framework rather than a standalone software product.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>ANN</t>
+          <t>DBN</t>
         </is>
       </c>
       <c r="B27">
-        <v>64</v>
+        <v>18</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1432,27 +1432,27 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Artificial Neural Network (ANN) is a general machine‑learning algorithm that can be applied to many tasks, including sentiment or opinion analysis, but it is not specifically designed for opinion measurement and is not itself a reusable software package.</t>
+          <t>Deep Belief Network (DBN) is a generative neural network architecture primarily used for unsupervised feature learning and classification. It is a general machine learning algorithm rather than a specific software product or opinion-specific tool.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>fastText</t>
+          <t>DCNN</t>
         </is>
       </c>
       <c r="B28">
-        <v>58</v>
+        <v>11</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>general_purpose_nlp</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1462,37 +1462,37 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>fastText is an open‑source library for learning word embeddings and performing fast text classification. It can be applied to opinion/sentiment analysis but is not built specifically for that purpose.</t>
+          <t>DCNN (Deep Convolutional Neural Network) is a general neural network architecture used for feature extraction and classification across various domains, including text analysis, but it is not a specific software product or opinion measurement tool itself.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LIWC</t>
+          <t>DNN</t>
         </is>
       </c>
       <c r="B29">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>single_purpose_nlp</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1502,32 +1502,32 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>LIWC (Linguistic Inquiry and Word Count) is a proprietary software tool that uses a psycholinguistic dictionary to quantify affective and cognitive dimensions in text, enabling both general and specifically designed opinion/sentiment measurement.</t>
+          <t>DNN (Deep Neural Network) refers to a general class of machine learning architectures composed of multiple interconnected layers. It is a foundational algorithmic paradigm used across various domains for pattern recognition and prediction, but is not a specific software package or dedicated opinion measurement tool.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tweepy</t>
+          <t>Decision Tree</t>
         </is>
       </c>
       <c r="B30">
-        <v>54</v>
+        <v>135</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>data_collection</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1537,7 +1537,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1547,27 +1547,27 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Tweepy is a Python library that provides an interface to the Twitter API for collecting tweets and other Twitter data. It does not perform opinion measurement itself.</t>
+          <t>Decision Tree is a general machine learning algorithm used for classification and regression tasks. While it can be applied to opinion measurement by classifying text features, it is not specifically designed for opinion analysis nor is it a standalone software product.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>XGBoost</t>
+          <t>Deep Learning</t>
         </is>
       </c>
       <c r="B31">
-        <v>52</v>
+        <v>27</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>approach</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1577,7 +1577,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1587,23 +1587,23 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>XGBoost is a gradient‑boosted decision tree algorithm with an open‑source library implementation. It can be applied to opinion/sentiment classification tasks but is not designed specifically for opinion measurement.</t>
+          <t>Deep learning is a broad machine learning paradigm and conceptual approach rather than a specific software product. It encompasses various architectures and algorithms used to perform text representation, classification, and target identification in opinion measurement pipelines.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RoBERTa</t>
+          <t>DistilBERT</t>
         </is>
       </c>
       <c r="B32">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -1632,22 +1632,22 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>RoBERTa is a pre‑trained transformer language model that can be fine‑tuned for many NLP tasks, including sentiment or opinion analysis, but it is not specifically built for opinion measurement.</t>
+          <t>DistilBERT is a lightweight, pre-trained transformer language model distilled from BERT. It generates contextual text representations and can be fine-tuned for classification tasks, but it is a general-purpose model rather than a tool specifically designed for opinion measurement.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>MLP</t>
+          <t>ELMo</t>
         </is>
       </c>
       <c r="B33">
-        <v>50</v>
+        <v>14</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>model</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1672,22 +1672,22 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>MLP (Multi‑Layer Perceptron) is a general neural‑network learning algorithm that can be applied to many classification problems, including sentiment or opinion analysis, but it is not specifically built for opinion measurement.</t>
+          <t>ELMo (Embeddings from Language Models) is a pre-trained deep contextualized word representation model that generates context-aware numerical embeddings for words. It is specifically designed for text representation and serves as a feature extractor for downstream tasks, but does not perform classification or target identification on its own.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Twitter API</t>
+          <t>GCN</t>
         </is>
       </c>
       <c r="B34">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>data_collection</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1697,7 +1697,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1712,67 +1712,67 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>The Twitter API is an interface for collecting tweets and other data from the Twitter platform. It enables data gathering but does not itself perform opinion measurement.</t>
+          <t>Graph Convolutional Network is a deep learning architecture designed for processing graph-structured data. It is a general-purpose algorithm that can be adapted for text classification or representation learning but is not specifically designed for opinion measurement.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>WEKA</t>
+          <t>GRU</t>
         </is>
       </c>
       <c r="B35">
-        <v>49</v>
+        <v>78</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>gui_tool</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>WEKA is a GUI‑based suite of machine learning algorithms for data mining; it can be employed to build opinion/sentiment classifiers but is not specifically designed for opinion measurement.</t>
+          <t>GRU (Gated Recurrent Unit) is a recurrent neural network architecture used for sequence modeling. It is a general-purpose algorithmic building block rather than a specific software product or a tool designed exclusively for opinion measurement tasks.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SenticNet</t>
+          <t>Gaussian Naive Bayes</t>
         </is>
       </c>
       <c r="B36">
-        <v>48</v>
+        <v>11</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>linguistic_resource</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1792,22 +1792,22 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>SenticNet is a concept‑level sentiment knowledge base that provides affective scores for terms and multi‑word expressions. It is specifically created for sentiment/opinion analysis, but it is a lexical resource rather than installable software.</t>
+          <t>Gaussian Naive Bayes is a probabilistic machine learning algorithm used for classification tasks. While it can be applied to opinion measurement when paired with appropriate text features, it is a general-purpose algorithm rather than a dedicated opinion measurement tool or installable software.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>WordNet</t>
+          <t>General Inquirer</t>
         </is>
       </c>
       <c r="B37">
-        <v>46</v>
+        <v>19</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>linguistic_resource</t>
+          <t>single_purpose_nlp</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1827,23 +1827,23 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>WordNet is a lexical database that provides semantic relationships between words; it is not specifically designed for opinion measurement and is not software itself.</t>
+          <t>General Inquirer is a dictionary-based text analysis program specifically designed to measure psychological, social, and cognitive processes, including sentiment and opinion, by matching text against predefined word lists. It provides a graphical interface for non-programmers to analyze text for affective and cognitive categories.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CNN-LSTM</t>
+          <t>Genetic Algorithm</t>
         </is>
       </c>
       <c r="B38">
-        <v>41</v>
+        <v>16</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -1852,17 +1852,17 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1872,22 +1872,22 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>CNN‑LSTM is a hybrid neural network architecture that combines convolutional layers with LSTM units. It can be applied to sentiment or opinion analysis but is a generic model design rather than a dedicated opinion‑measurement tool.</t>
+          <t>A metaheuristic optimization algorithm used to search for optimal solutions in complex parameter spaces. It is not specifically designed for opinion measurement or any of the three computational tasks, but can be used to tune hyperparameters or train other models.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AFINN</t>
+          <t>Gensim</t>
         </is>
       </c>
       <c r="B39">
-        <v>39</v>
+        <v>18</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>linguistic_resource</t>
+          <t>general_purpose_nlp</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1897,7 +1897,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1907,27 +1907,27 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>AFINN is a sentiment lexicon that assigns polarity scores to English words, designed specifically for sentiment and opinion analysis, but it is a data resource rather than installable software.</t>
+          <t>Gensim is a widely used Python library for unsupervised topic modeling and vector space modeling, primarily designed for text representation tasks like word and document embeddings. It is not specifically designed for opinion measurement or classification.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sentiment Analysis</t>
+          <t>GloVe</t>
         </is>
       </c>
       <c r="B40">
-        <v>38</v>
+        <v>103</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>approach</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1952,27 +1952,27 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Sentiment analysis is a high‑level methodological approach for detecting and quantifying evaluative attitudes in text, used broadly for opinion measurement but not a specific software package.</t>
+          <t>GloVe is an algorithm for generating word embeddings by factorizing a word-word co-occurrence matrix. It is specifically designed for text representation but does not perform classification or target identification.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>scikit-learn</t>
+          <t>Google Cloud Natural Language API</t>
         </is>
       </c>
       <c r="B41">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>general_library</t>
+          <t>commercial_api</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
@@ -1987,32 +1987,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>scikit-learn is a general‑purpose Python machine‑learning library that provides algorithms and utilities for classification, regression, and clustering. It can be employed to build opinion‑measurement models but is not specifically designed for that purpose.</t>
+          <t>Google Cloud Natural Language API is a commercial cloud service that provides NLP capabilities such as sentiment analysis, entity recognition, and content classification. It is accessed via a web API rather than installed locally and is primarily designed for classification and target identification tasks.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NRC Emotion Lexicon</t>
+          <t>Gradient Boosting</t>
         </is>
       </c>
       <c r="B42">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>linguistic_resource</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2032,32 +2032,32 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>The NRC Emotion Lexicon is a lexical resource that maps words to emotion categories (e.g., joy, anger). It can be used to infer affective opinions from text, making it applicable for opinion measurement, and it was created specifically for detecting emotions/feelings, a form of opinion measurement. It is not provided as installable software.</t>
+          <t>Gradient Boosting is a general-purpose machine learning ensemble algorithm used for classification and regression. While it can be applied to opinion measurement, it is not specifically designed for it and does not handle text representation or target identification directly.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>HMM</t>
         </is>
       </c>
       <c r="B43">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>programming_language</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2067,37 +2067,37 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Python is a general‑purpose programming language and runtime environment; it is not itself used for opinion measurement, but it can be used to implement such tools.</t>
+          <t>HMM (Hidden Markov Model) is a statistical algorithm used for modeling sequential data and making predictions based on hidden states. It is a general-purpose machine learning method that can be applied to various NLP tasks like sequence labeling, but it is not a specific software product or opinion measurement tool.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>BiGRU</t>
+          <t>HowNet</t>
         </is>
       </c>
       <c r="B44">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>linguistic_resource</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2112,18 +2112,18 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>BiGRU (Bidirectional Gated Recurrent Unit) is a neural network architecture that can be employed for sentiment or opinion analysis but is a general algorithm, not a dedicated opinion‑measurement tool.</t>
+          <t>HowNet is a computational dictionary and semantic knowledge base that represents word meanings using semantic primitives (sememes). It is primarily used for semantic analysis and word sense disambiguation rather than directly performing opinion measurement tasks.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Lexicon-based Sentiment Analysis</t>
+          <t>Hybrid Sentiment Analysis</t>
         </is>
       </c>
       <c r="B45">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2152,22 +2152,22 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Lexicon‑based sentiment analysis is a high‑level methodology that uses sentiment lexicons to detect and quantify opinions in text; it is specifically intended for opinion measurement but is not a concrete software package.</t>
+          <t>Hybrid Sentiment Analysis is a methodological approach that combines multiple techniques (e.g., lexicon-based and machine learning) to classify text sentiment. It is a conceptual framework rather than a specific software product, primarily designed for classification tasks.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Apache Hadoop</t>
+          <t>IAN</t>
         </is>
       </c>
       <c r="B46">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>infrastructure</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2177,33 +2177,33 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Apache Hadoop is an open‑source distributed computing framework for storing and processing large‑scale data. It provides the infrastructure for big‑data pipelines but does not itself perform opinion measurement.</t>
+          <t>IAN (Interactive Attention Networks) is a deep learning model architecture specifically designed for aspect-based sentiment analysis. It jointly performs target identification (aspect extraction) and classification (sentiment polarity), but it is a methodological framework rather than a packaged, installable software product.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SGD</t>
+          <t>J48</t>
         </is>
       </c>
       <c r="B47">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2212,12 +2212,12 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2232,37 +2232,37 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Stochastic Gradient Descent (SGD) is a general optimization algorithm used to train machine‑learning models, including those for sentiment or opinion analysis, but it is not itself a tool specifically designed for opinion measurement.</t>
+          <t>J48 is a decision tree algorithm implemented in the Weka machine learning toolkit, primarily used for classification tasks. It is a general-purpose machine learning method rather than a tool specifically designed for opinion measurement.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AdaBoost</t>
+          <t>JET</t>
         </is>
       </c>
       <c r="B48">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>model</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2272,58 +2272,58 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>AdaBoost is a general ensemble learning algorithm that can be applied to classification problems, including sentiment or opinion detection, but it is not specifically designed for opinion measurement and is not itself a software package.</t>
+          <t>JET (Joint Entity and Target) is a deep learning model designed for aspect-based sentiment analysis that jointly identifies target aspects and classifies their associated sentiments. It is a research architecture shared as code rather than a standalone installable software package.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Bag-of-Words</t>
+          <t>JST</t>
         </is>
       </c>
       <c r="B49">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>approach</t>
+          <t>single_purpose_nlp</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>unclear</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Bag‑of‑Words is a general text representation approach that can be used as features for opinion/sentiment classification, but it is not a dedicated opinion‑measurement tool nor provided as installable software.</t>
+          <t>JST likely refers to the Japanese Sentiment Tool, a dedicated software package designed for opinion and sentiment analysis in Japanese text. It is primarily used for sentiment classification, while its specific capabilities regarding text representation and target identification are not fully specified in standard documentation.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DNN</t>
+          <t>KNN</t>
         </is>
       </c>
       <c r="B50">
-        <v>27</v>
+        <v>93</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -2332,12 +2332,12 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2352,27 +2352,27 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>DNN (Deep Neural Network) is a general machine‑learning architecture that can be applied to many tasks, including sentiment or opinion analysis, but it is not a specific tool or software designed solely for opinion measurement.</t>
+          <t>K-Nearest Neighbors (KNN) is a general-purpose supervised machine learning algorithm primarily used for classification and regression. While it can be applied to opinion measurement when paired with numerical text features, it is not specifically designed for opinion analysis nor is it a standalone software product.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Deep Learning</t>
+          <t>Keras</t>
         </is>
       </c>
       <c r="B51">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>approach</t>
+          <t>general_library</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2387,23 +2387,23 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Deep Learning is a high‑level methodological approach for building neural network models; it can be applied to opinion measurement but is not itself a specific opinion‑measurement tool.</t>
+          <t>Keras is an open-source deep learning framework/library for building and training neural networks. It is a general-purpose tool not specifically designed for opinion measurement or any of the three specific tasks, but can be used to implement models that perform them.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>ATAE-LSTM</t>
+          <t>LDA</t>
         </is>
       </c>
       <c r="B52">
-        <v>26</v>
+        <v>167</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>ATAE‑LSTM is an attention‑based LSTM architecture for aspect‑based sentiment analysis, i.e., a model architecture that can be used to extract opinions from text but is not distributed as a ready‑to‑install software package.</t>
+          <t>Latent Dirichlet Allocation is a generative probabilistic algorithm primarily used for topic modeling. It converts text into document-topic numerical representations and performs unsupervised topic classification, but it does not identify specific opinion targets within the text.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>LSA</t>
+          <t>LIWC</t>
         </is>
       </c>
       <c r="B53">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>single_purpose_nlp</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2467,23 +2467,23 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Latent Semantic Analysis (LSA) is a statistical algorithm for extracting and representing the underlying semantic structure of text. It can be incorporated into opinion‑measurement pipelines but is not specifically designed for that purpose.</t>
+          <t>LIWC (Linguistic Inquiry and Word Count) is a dictionary-based text analysis software that categorizes words into predefined psychological, social, and cognitive categories. It is specifically designed for linguistic and psychological text analysis rather than direct opinion measurement, but is widely used for inferring author attitudes and emotions.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Gradient Boosting</t>
+          <t>LSA</t>
         </is>
       </c>
       <c r="B54">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2512,67 +2512,67 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Gradient Boosting is a general ensemble learning algorithm that can be applied to classification tasks such as sentiment or opinion analysis, but it is not specifically designed for opinion measurement.</t>
+          <t>Latent Semantic Analysis (LSA) is a mathematical algorithm that extracts latent semantic structures from text by applying dimensionality reduction (typically SVD) to produce dense numerical vector representations. It is specifically designed for text representation and does not perform classification or target identification, nor is it a standalone software product.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>IAN</t>
+          <t>LSTM</t>
         </is>
       </c>
       <c r="B55">
-        <v>25</v>
+        <v>352</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>other_unclear</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>The term "IAN" lacks sufficient context to determine its nature (e.g., tool, algorithm, resource) or its applicability to opinion measurement.</t>
+          <t>LSTM (Long Short-Term Memory) is a recurrent neural network architecture designed for processing sequential data. It is a general-purpose deep learning algorithm rather than a specific software product, and is commonly used for sequence classification tasks such as sentiment or opinion analysis.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Bing Liu Opinion Lexicon</t>
+          <t>Lexicon-based Sentiment Analysis</t>
         </is>
       </c>
       <c r="B56">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>linguistic_resource</t>
+          <t>approach</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2592,22 +2592,22 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>The Bing Liu Opinion Lexicon is a curated list of positive and negative opinion words used for sentiment and opinion analysis. It is a lexical resource specifically designed for opinion measurement, not a software package.</t>
+          <t>Lexicon-based sentiment analysis is a methodological approach that uses pre-defined dictionaries to assign sentiment scores or labels to text. It is a conceptual framework rather than a specific installable software product.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>R</t>
+          <t>LightGBM</t>
         </is>
       </c>
       <c r="B57">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>programming_language</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2627,23 +2627,23 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>R is a general-purpose programming language and environment for statistical computing. It can be used to implement opinion measurement methods via packages, but the language itself is not a tool specifically designed for opinion measurement.</t>
+          <t>LightGBM is a gradient boosting framework that uses tree-based learning algorithms. It is a general-purpose machine learning algorithm primarily used for classification and regression tasks, not specifically designed for opinion measurement or NLP.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>k-means</t>
+          <t>LinearSVC</t>
         </is>
       </c>
       <c r="B58">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2672,58 +2672,58 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>k-means is a general clustering algorithm used for grouping data points; it is not specifically designed for opinion measurement and is not provided as standalone software.</t>
+          <t>LinearSVC is a linear kernel Support Vector Classifier algorithm used for binary and multiclass classification tasks. It is a general-purpose machine learning method that can be applied to opinion measurement when paired with text representation techniques, but it is not specifically designed for it.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>RapidMiner</t>
+          <t>Logistic Regression</t>
         </is>
       </c>
       <c r="B59">
-        <v>22</v>
+        <v>196</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>gui_tool</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>RapidMiner is a visual data science platform that provides a GUI for building and executing machine‑learning pipelines, including sentiment or opinion analysis via extensions. It can be used for opinion measurement but is not purpose‑built for it.</t>
+          <t>Logistic Regression is a general-purpose statistical and machine learning algorithm primarily used for classification tasks. While it can be applied to opinion measurement when paired with text feature extraction, it is a mathematical method rather than a dedicated software product or specifically designed for opinion analysis.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TD-LSTM</t>
+          <t>MLP</t>
         </is>
       </c>
       <c r="B60">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2752,27 +2752,27 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>TD‑LSTM (Target‑Dependent LSTM) is a neural network architecture proposed for target‑specific sentiment analysis. It can be applied to opinion measurement in general and was specifically designed for that purpose, but it is described as an algorithmic model rather than a released software package.</t>
+          <t>MLP (Multi-Layer Perceptron) is a general feedforward neural network architecture used for machine learning tasks like classification and regression. It is a mathematical model rather than a specific software product, though it can be implemented in various libraries.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>doc2vec</t>
+          <t>MPQA</t>
         </is>
       </c>
       <c r="B61">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>linguistic_resource</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2792,32 +2792,32 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>doc2vec (Paragraph Vector) is a general algorithm for learning fixed‑length vector representations of documents. It can be used as features for opinion/sentiment classification, but it is not specifically designed for opinion measurement and is not itself a reusable software package.</t>
+          <t>MPQA refers to the Multi-Perspective Question Answering Subjectivity Corpus, a widely used dataset for training and evaluating opinion mining and sentiment analysis models. It contains manually annotated text with subjectivity, polarity, and target annotations but is not itself a software tool or algorithm.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Bernoulli Naive Bayes</t>
+          <t>Machine Learning</t>
         </is>
       </c>
       <c r="B62">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>approach</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2832,18 +2832,18 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Bernoulli Naive Bayes is a probabilistic classification algorithm that can be applied to binary feature vectors, often used for text classification tasks such as sentiment analysis, but it is not specifically designed for opinion measurement.</t>
+          <t>Machine Learning is a broad computational paradigm and research field focused on building systems that learn patterns from data, rather than a specific software product or opinion measurement tool. While it underpins many classification and representation techniques, it is not specifically designed for any of the three opinion measurement tasks.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>JST</t>
+          <t>Maximum Entropy</t>
         </is>
       </c>
       <c r="B63">
-        <v>21</v>
+        <v>69</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -2852,7 +2852,7 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2862,37 +2862,37 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>JST (Joint Sentiment‑Topic) is a probabilistic model that jointly discovers topics and sentiment in text, specifically designed for opinion measurement, but it is primarily a modeling approach rather than a packaged software tool.</t>
+          <t>Maximum Entropy is a general machine learning algorithm used for classification tasks. While it can be applied to opinion measurement, it is not specifically designed for it and does not produce text representations or target spans.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MPQA</t>
+          <t>MeaningCloud</t>
         </is>
       </c>
       <c r="B64">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>linguistic_resource</t>
+          <t>commercial_api</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2912,22 +2912,22 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>MPQA (Multi‑Perspective Question Answering) includes a subjectivity lexicon and opinion corpus designed for detecting subjective expressions and sentiment. It is a lexical/resource asset, not a software package, but it is specifically created for opinion measurement.</t>
+          <t>MeaningCloud is a commercial cloud-based API that provides NLP services such as sentiment analysis, topic extraction, and entity recognition. It is accessed remotely via web services rather than installed locally.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Keras</t>
+          <t>MemNet</t>
         </is>
       </c>
       <c r="B65">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>general_library</t>
+          <t>model</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2937,7 +2937,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2947,32 +2947,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Keras is a high‑level deep‑learning library for building neural network models. It can be used to create opinion‑measurement models (e.g., sentiment classifiers) but is not itself a dedicated opinion‑measurement tool.</t>
+          <t>MemNet is a memory-augmented neural network architecture specifically designed for aspect-based sentiment analysis, jointly identifying opinion targets and classifying their sentiment polarity. It is a research model rather than a packaged software product.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>General Inquirer</t>
+          <t>Multinomial Naive Bayes</t>
         </is>
       </c>
       <c r="B66">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>linguistic_resource</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2982,7 +2982,7 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -2992,22 +2992,22 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>The General Inquirer is a lexical resource that provides word categories, including positive/negative sentiment, and is used for opinion and sentiment analysis, but it is a data resource rather than installable software.</t>
+          <t>Multinomial Naive Bayes is a probabilistic machine learning algorithm widely used for text classification tasks, including sentiment and opinion analysis. It operates on discrete feature counts (like word frequencies) but does not inherently generate text representations or identify specific targets within the text.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SVC</t>
+          <t>NLTK</t>
         </is>
       </c>
       <c r="B67">
-        <v>19</v>
+        <v>101</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>general_purpose_nlp</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -3017,33 +3017,33 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>SVC (Support Vector Classifier) is a machine‑learning algorithm for binary/multi‑class classification that can be applied to sentiment or opinion detection, but it is not a tool specifically built for opinion measurement.</t>
+          <t>Natural Language Toolkit is a comprehensive Python library for NLP tasks including tokenization, POS tagging, and sentiment analysis. It can be used for opinion measurement but is not specifically designed for it.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DBN</t>
+          <t>NMF</t>
         </is>
       </c>
       <c r="B68">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -3072,32 +3072,32 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>DBN (Deep Belief Network) is a general neural network learning algorithm that can be applied to various classification tasks, including sentiment or opinion analysis, but it is not specifically designed for opinion measurement and is not provided as a standalone software package.</t>
+          <t>Non-negative Matrix Factorization is a mathematical algorithm used for dimensionality reduction and feature extraction, commonly applied to document-term matrices for topic modeling or text representation. It is a general method rather than a standalone software product.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Gensim</t>
+          <t>NRC Emotion Lexicon</t>
         </is>
       </c>
       <c r="B69">
-        <v>18</v>
+        <v>37</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>general_purpose_nlp</t>
+          <t>linguistic_resource</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -3107,27 +3107,27 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Gensim is a Python library for topic modeling, word embeddings, and similarity analysis. It can be used as a component in opinion‑measurement pipelines but is not itself designed for extracting opinions.</t>
+          <t>The NRC Emotion Lexicon is a widely used lexical resource that maps words to eight basic emotions and positive/negative sentiment scores. It functions as a dictionary-based classification tool rather than installable software or a system for text representation or target identification.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SMOTE</t>
+          <t>NTUSD</t>
         </is>
       </c>
       <c r="B70">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>linguistic_resource</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -3152,22 +3152,22 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>SMOTE (Synthetic Minority Over-sampling Technique) is a data‑augmentation algorithm for handling class imbalance. It is not designed to extract or measure opinions from text, nor is it provided as a standalone software package.</t>
+          <t>NTUSD (National Taiwan University Sentiment Dictionary) is a widely used Chinese sentiment lexicon that provides polarity scores for words. It serves as a linguistic resource for opinion measurement rather than a software tool.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Stanford Parser</t>
+          <t>NVivo</t>
         </is>
       </c>
       <c r="B71">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>single_purpose_nlp</t>
+          <t>gui_tool</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3192,27 +3192,27 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Stanford Parser is a dedicated syntactic parsing tool that produces constituency parse trees. It can be used as a component in opinion‑analysis pipelines but is not itself designed for measuring opinions.</t>
+          <t>NVivo is a commercial qualitative data analysis software with a graphical interface used for organizing, coding, and analyzing textual data. While it supports manual and semi-automated thematic analysis, it is not specifically designed for computational opinion measurement tasks like automatic sentiment classification or target identification.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>ABSA</t>
+          <t>Naive Bayes</t>
         </is>
       </c>
       <c r="B72">
-        <v>17</v>
+        <v>531</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>approach</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3232,22 +3232,22 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>ABSA (Aspect‑Based Sentiment Analysis) is a high‑level methodology for extracting opinions about specific aspects of a target, making it a general and specifically designed opinion measurement approach, but it is not a standalone software package.</t>
+          <t>Naive Bayes is a probabilistic machine learning algorithm used for classification tasks. While it can be applied to opinion measurement by classifying text sentiment or stance, it is a general algorithm rather than a dedicated tool or software package.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Apache Spark</t>
+          <t>Natural Language Processing</t>
         </is>
       </c>
       <c r="B73">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>infrastructure</t>
+          <t>approach</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -3262,68 +3262,68 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Apache Spark is an open‑source distributed computing framework for large‑scale data processing. It does not itself perform opinion measurement, though it can be used as a platform to run sentiment‑analysis pipelines.</t>
+          <t>Natural Language Processing is a broad academic field and conceptual approach rather than a specific software tool or framework. It encompasses the study of algorithms for text processing but is not itself a dedicated opinion measurement tool.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Genetic Algorithm</t>
+          <t>OpinionFinder</t>
         </is>
       </c>
       <c r="B74">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>single_purpose_nlp</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Genetic Algorithm is a general-purpose optimization metaheuristic that can be applied to various problems, including training classifiers for sentiment or opinion analysis, but it is not specifically designed for opinion measurement and is not itself a software package.</t>
+          <t>OpinionFinder is a dedicated NLP software package designed to extract subjective language, classify opinion polarity, and identify opinion targets within text. It is distributed as an installable tool rather than a numerical text representation method.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>J48</t>
+          <t>PSO</t>
         </is>
       </c>
       <c r="B75">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -3332,7 +3332,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3352,27 +3352,27 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>J48 is an implementation of the C4.5 decision‑tree algorithm (commonly used in WEKA). It is a general classification algorithm that can be applied to opinion/sentiment tasks but is not specifically designed for opinion measurement.</t>
+          <t>PSO (Particle Swarm Optimization) is a general metaheuristic optimization algorithm inspired by social behavior. It is not specifically designed for opinion measurement or any of the three core tasks, but can be used to optimize model parameters or hyperparameters.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>LinearSVC</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="B76">
-        <v>16</v>
+        <v>37</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>programming_language</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3387,32 +3387,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>LinearSVC is a linear Support Vector Classification algorithm (often accessed via scikit‑learn). It can be applied to sentiment or opinion classification tasks but is not specifically built for opinion measurement and is not a standalone software package.</t>
+          <t>Python is a general-purpose programming language used for software development and scripting. While it can be used to implement opinion measurement pipelines, it is not specifically designed for any of the three computational tasks.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Machine Learning</t>
+          <t>R</t>
         </is>
       </c>
       <c r="B77">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>approach</t>
+          <t>programming_language</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3427,27 +3427,27 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Machine learning is a broad methodological approach for building predictive models, which can be applied to opinion measurement tasks but is not itself a software tool nor specifically designed for opinion analysis.</t>
+          <t>R is a general-purpose programming language and environment for statistical computing. While it can be used to implement opinion measurement pipelines via various packages, it is not specifically designed for opinion measurement itself.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Sentiment140</t>
+          <t>RNN</t>
         </is>
       </c>
       <c r="B78">
-        <v>16</v>
+        <v>118</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>linguistic_resource</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -3472,18 +3472,18 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>Sentiment140 is a corpus of 1.6 million tweets annotated with sentiment labels, used as a resource for training/evaluating sentiment analysis models rather than as a software tool.</t>
+          <t>RNN (Recurrent Neural Network) is a general-purpose neural network architecture designed for processing sequential data. It is a mathematical model rather than installable software, and while it can be adapted for classification or representation tasks, it is not specifically designed for opinion measurement.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Transformer</t>
+          <t>Random Forest</t>
         </is>
       </c>
       <c r="B79">
-        <v>16</v>
+        <v>260</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -3492,7 +3492,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3512,22 +3512,22 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>The Transformer is a neural network architecture (algorithm) that underlies many modern NLP models. It can be employed for opinion measurement when fine‑tuned, but it is not itself a tool specifically designed for that purpose and is not provided as standalone software.</t>
+          <t>Random Forest is a supervised machine learning algorithm that combines multiple decision trees to make predictions. It is widely used for classification tasks like sentiment analysis but is a general-purpose algorithm rather than a dedicated opinion measurement tool or installable software.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>BiLSTM-CRF</t>
+          <t>RapidMiner</t>
         </is>
       </c>
       <c r="B80">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>gui_tool</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3537,37 +3537,37 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>BiLSTM‑CRF is a neural network architecture (bidirectional LSTM with a CRF layer) used for sequence labeling; it can be trained for opinion‑related tasks (e.g., aspect extraction) but is not itself a dedicated opinion‑measurement tool and is not a packaged software.</t>
+          <t>RapidMiner is a comprehensive, GUI-based data science platform that enables users to build machine learning and text mining workflows through a drag-and-drop interface. It supports the full opinion measurement pipeline, including text representation, classification, and target identification, without requiring programming.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>MemNet</t>
+          <t>Recursive Neural Network</t>
         </is>
       </c>
       <c r="B81">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -3582,7 +3582,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3592,22 +3592,22 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>MemNet (Memory Network) is a deep neural model introduced for sentiment analysis; it can be used to infer opinions from text and was specifically designed for that purpose, but it is a pre‑trained model rather than a standalone installable software package.</t>
+          <t>Recursive Neural Network is a neural network architecture designed to process tree-structured data by recursively combining child vectors into parent vectors. It serves as a general algorithm for learning phrase-level text representations and performing classification tasks like sentiment analysis, rather than a specific installable software product.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>OpinionFinder</t>
+          <t>RoBERTa</t>
         </is>
       </c>
       <c r="B82">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>single_purpose_nlp</t>
+          <t>model</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3622,37 +3622,37 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>OpinionFinder is a dedicated software system specifically designed to detect and analyze subjective language and opinions in text.</t>
+          <t>RoBERTa is a pre-trained transformer language model optimized for masked language modeling. It is widely used as a foundation for various NLP tasks, including opinion measurement, but is not specifically designed for it.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Word Embeddings</t>
+          <t>SGD</t>
         </is>
       </c>
       <c r="B83">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3672,37 +3672,37 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Word embeddings are pre‑trained vector representations of words (e.g., Word2Vec, GloVe). They can be used as features for opinion measurement but are not specifically designed for that purpose and are not software themselves.</t>
+          <t>Stochastic Gradient Descent is a general optimization algorithm used to minimize loss functions during model training. It is not specifically designed for opinion measurement or any specific NLP task, nor is it a standalone software product.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>XLNet</t>
+          <t>SMOTE</t>
         </is>
       </c>
       <c r="B84">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3712,77 +3712,77 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>XLNet is a pre‑trained autoregressive language model that can be fine‑tuned for various NLP tasks, including sentiment or opinion analysis, but it is not specifically built for opinion measurement.</t>
+          <t>SMOTE (Synthetic Minority Over-sampling Technique) is a general machine learning algorithm used to address class imbalance by generating synthetic samples for minority classes. It is not specifically designed for opinion measurement or text processing, but can be used as a preprocessing step to improve classification performance.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>spaCy</t>
+          <t>SVC</t>
         </is>
       </c>
       <c r="B85">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>general_purpose_nlp</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>spaCy is a comprehensive Python library for NLP tasks such as tokenization, parsing, and named entity recognition, and it can be extended for opinion/sentiment analysis, though it is not built specifically for that purpose.</t>
+          <t>SVC (Support Vector Classifier) is a machine learning algorithm used for classification tasks. It is a mathematical method rather than a standalone software product, requires pre-processed numerical features as input, and does not handle text representation or target identification.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>ELMo</t>
+          <t>SVM</t>
         </is>
       </c>
       <c r="B86">
-        <v>14</v>
+        <v>646</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3792,32 +3792,32 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>ELMo (Embeddings from Language Models) is a pre‑trained contextual word‑embedding model that can be used as features for sentiment or opinion analysis, but it is not specifically built for opinion measurement.</t>
+          <t>A general machine learning algorithm used for classification tasks, including sentiment and opinion analysis, but not specifically designed for opinion measurement nor is it a standalone software product.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>PSO</t>
+          <t>SentiStrength</t>
         </is>
       </c>
       <c r="B87">
-        <v>14</v>
+        <v>78</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>single_purpose_nlp</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3827,27 +3827,27 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Particle Swarm Optimization (PSO) is a general meta‑heuristic optimization algorithm. It can be used to train models for many tasks, including sentiment analysis, but it is not itself a tool for extracting opinions from text and is not specifically designed for opinion measurement.</t>
+          <t>SentiStrength is a dedicated, rule-based sentiment analysis tool specifically designed for opinion measurement. It outputs positive and negative sentiment scores for text but does not perform text representation or target identification. It is distributed as a standalone Java application and library.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Apache Hadoop MapReduce</t>
+          <t>SentiWordNet</t>
         </is>
       </c>
       <c r="B88">
-        <v>13</v>
+        <v>211</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>infrastructure</t>
+          <t>linguistic_resource</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3857,47 +3857,47 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Apache Hadoop MapReduce is a distributed computing framework for processing large data sets. It is not itself an opinion measurement tool, though it can be used to run opinion analysis pipelines.</t>
+          <t>SentiWordNet is a lexical resource that assigns sentiment scores to WordNet synsets. It is specifically designed for sentiment and opinion analysis but functions as a data resource rather than installable software.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>CNN-BiLSTM</t>
+          <t>SenticNet</t>
         </is>
       </c>
       <c r="B89">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>linguistic_resource</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3912,27 +3912,27 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>CNN‑BiLSTM is a neural network architecture that combines convolutional layers with a bidirectional LSTM. It can be applied to opinion/sentiment analysis but is not itself a dedicated opinion‑measurement tool, nor is it a packaged software component.</t>
+          <t>SenticNet is a semantic knowledge base and lexical resource designed for sentiment analysis and opinion mining. It provides sentiment scores and semantic relations for concepts but is not a software product itself.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Google Cloud Natural Language API</t>
+          <t>Sentiment Analysis</t>
         </is>
       </c>
       <c r="B90">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>commercial_api</t>
+          <t>approach</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3942,28 +3942,28 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Google Cloud Natural Language API is a cloud‑based commercial service that provides NLP functions including sentiment analysis, enabling general and specific opinion measurement via an API.</t>
+          <t>Sentiment analysis is a high-level computational approach or task focused on classifying text into evaluative categories (e.g., positive, negative, neutral). It is not a specific software product but a general methodology implemented by various tools, models, and algorithms.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>NTUSD</t>
+          <t>Sentiment140</t>
         </is>
       </c>
       <c r="B91">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -3972,12 +3972,12 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3992,22 +3992,22 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>NTUSD (National Taiwan University Sentiment Dictionary) is a Chinese sentiment lexicon that provides polarity scores for words, designed specifically for sentiment and opinion analysis but distributed as a data resource rather than installable software.</t>
+          <t>Sentiment140 is a widely used corpus of 1.6 million tweets labeled with positive or negative sentiment. It serves as a benchmark dataset for training and evaluating sentiment analysis models rather than a software tool or algorithm itself.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>T5</t>
+          <t>SnowNLP</t>
         </is>
       </c>
       <c r="B92">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>general_purpose_nlp</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4022,32 +4022,32 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>T5 (Text‑to‑Text Transfer Transformer) is a pre‑trained language model that can be fine‑tuned for many downstream tasks, including sentiment or opinion analysis, but it is not built specifically for opinion measurement.</t>
+          <t>SnowNLP is a Python library for processing Chinese text that provides tokenization, POS tagging, TF-IDF, and a built-in sentiment analysis module. It is distributed as an installable package and supports a range of NLP tasks rather than focusing on a single function.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>XLM-RoBERTa</t>
+          <t>Stanford CoreNLP</t>
         </is>
       </c>
       <c r="B93">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>general_purpose_nlp</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4067,19 +4067,19 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>XLM‑RoBERTa is a pre‑trained multilingual transformer model that can be fine‑tuned for various NLP tasks, including sentiment or opinion analysis, but it is not specifically built for opinion measurement.</t>
+          <t>Stanford CoreNLP is a comprehensive, open-source Java library that provides a wide range of natural language processing capabilities, including tokenization, POS tagging, parsing, sentiment analysis, and named entity recognition. It serves as a general-purpose toolkit rather than a dedicated opinion measurement tool.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>GCN</t>
+          <t>Stanford POS Tagger</t>
         </is>
       </c>
       <c r="B94">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>single_purpose_nlp</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -4102,37 +4102,37 @@
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>GCN (Graph Convolutional Network) is a general neural network architecture for learning on graph-structured data. It can be applied to opinion/sentiment analysis tasks but is not specifically built for opinion measurement, and it is an algorithm rather than a standalone software package.</t>
+          <t>Stanford POS Tagger is a dedicated software tool for assigning part-of-speech tags to words in text. It performs classification by labeling grammatical categories but does not handle text representation or opinion target identification.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>MeaningCloud</t>
+          <t>Stanford Parser</t>
         </is>
       </c>
       <c r="B95">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>commercial_api</t>
+          <t>single_purpose_nlp</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -4142,7 +4142,7 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -4152,22 +4152,22 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>MeaningCloud is a commercial cloud‑based API that offers text analytics services such as sentiment and opinion analysis, making it directly usable for measuring opinions.</t>
+          <t>Stanford Parser is a dedicated NLP software tool primarily used for part-of-speech tagging and syntactic parsing. It assigns linguistic labels to text but is not specifically designed for opinion measurement or numerical text representation.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Stanford POS Tagger</t>
+          <t>T5</t>
         </is>
       </c>
       <c r="B96">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>single_purpose_nlp</t>
+          <t>model</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4177,7 +4177,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>The Stanford POS Tagger is a dedicated tool for part‑of‑speech tagging of text. It is software that can be installed and run, but it is not designed for opinion measurement.</t>
+          <t>T5 (Text-to-Text Transfer Transformer) is a pre-trained language model that frames all NLP tasks as text-to-text problems. It is widely used for text representation and classification via fine-tuning, but is not specifically designed for target identification.</t>
         </is>
       </c>
     </row>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4232,27 +4232,27 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>TC‑LSTM (Target‑Conditioned LSTM) is a neural network architecture designed for target‑dependent sentiment (opinion) analysis. It can be used for general opinion measurement and is specifically built for that purpose, but it is an algorithmic description rather than a packaged, installable software tool.</t>
+          <t>TC-LSTM (Target-Context LSTM) is a neural network architecture specifically designed for aspect-based sentiment analysis, focusing on jointly modeling target and context to classify sentiment. It is a research model rather than a standalone software package.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>ASUM</t>
+          <t>TD-LSTM</t>
         </is>
       </c>
       <c r="B98">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4262,28 +4262,28 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>unclear</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>ASUM (Aspect and Sentiment Unification Model) is a probabilistic model designed for joint aspect extraction and sentiment analysis, i.e., opinion measurement. It can be used for opinion measurement in general and is specifically built for that purpose, though it is unclear whether a reusable, installable software package is publicly available.</t>
+          <t>TD-LSTM (Target-Dependent Long Short-Term Memory) is a neural network architecture specifically designed for aspect-based sentiment classification. It takes a target/aspect as input alongside text to predict sentiment labels, but it is a model architecture rather than a standalone installable software package.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AT-LSTM</t>
+          <t>TF-IDF</t>
         </is>
       </c>
       <c r="B99">
-        <v>11</v>
+        <v>113</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -4312,14 +4312,14 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>AT-LSTM is an attention‑based LSTM architecture proposed for aspect‑level sentiment (opinion) analysis. It can be used to measure opinions in text and is specifically designed for that purpose, but it is described as a model architecture rather than a packaged, installable software tool.</t>
+          <t>TF-IDF is a statistical algorithm specifically designed for text representation and feature extraction. It converts text into numerical vectors based on term frequency but is a mathematical method rather than a standalone software product.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Apache OpenNLP</t>
+          <t>TensorFlow</t>
         </is>
       </c>
       <c r="B100">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>general_purpose_nlp</t>
+          <t>general_library</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4342,7 +4342,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -4352,32 +4352,32 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Apache OpenNLP is an open‑source Java library offering a range of NLP components (tokenizer, POS tagger, NER, parser, etc.). It can be employed for opinion/sentiment analysis but is not built specifically for that purpose.</t>
+          <t>TensorFlow is a general-purpose open-source machine learning framework used for building and training deep learning models. While it can be used to implement opinion measurement pipelines, it is not specifically designed for text representation, classification, or target identification, nor is it NLP-specific.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Attention-BiLSTM</t>
+          <t>TextBlob</t>
         </is>
       </c>
       <c r="B101">
-        <v>11</v>
+        <v>134</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>general_purpose_nlp</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -4387,23 +4387,23 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Attention‑BiLSTM is a neural network architecture (bidirectional LSTM with an attention mechanism) that can be applied to many text classification tasks, including sentiment or opinion analysis, but it is not a ready‑to‑use software package nor specifically built for opinion measurement.</t>
+          <t>TextBlob is a popular Python library that simplifies common NLP tasks such as part-of-speech tagging, noun phrase extraction, and sentiment analysis. It provides document- or sentence-level sentiment scores and classification capabilities but does not specifically extract or identify opinion targets.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Bayesian Network</t>
+          <t>Transformer</t>
         </is>
       </c>
       <c r="B102">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -4417,12 +4417,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
@@ -4432,27 +4432,27 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>A Bayesian Network is a probabilistic graphical model used for reasoning under uncertainty; it can be applied to opinion measurement tasks but is a general algorithmic framework, not a dedicated opinion‑measurement tool, and it is not itself a software package.</t>
+          <t>The Transformer is a neural network architecture based on self-attention mechanisms, introduced for sequence modeling. It serves as a foundational algorithm for generating contextual representations and performing classification or target identification, but it is a mathematical framework rather than a specific software product.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>DCNN</t>
+          <t>Tweepy</t>
         </is>
       </c>
       <c r="B103">
-        <v>11</v>
+        <v>54</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>data_collection</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4467,42 +4467,42 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>DCNN (Deep Convolutional Neural Network) is a neural network architecture that can be applied to many text classification tasks, including sentiment or opinion analysis, but it is not a tool specifically designed for opinion measurement.</t>
+          <t>Tweepy is a Python library that provides a convenient interface to the Twitter API for fetching, posting, and streaming social media data. It is designed for data collection rather than opinion measurement or text analysis.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DistilBERT</t>
+          <t>Twitter API</t>
         </is>
       </c>
       <c r="B104">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>model</t>
+          <t>data_collection</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -4512,27 +4512,27 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>DistilBERT is a pre‑trained, distilled transformer model derived from BERT. It can be fine‑tuned for sentiment or opinion analysis, but it is a generic language model rather than a tool built specifically for opinion measurement.</t>
+          <t>An API for collecting data from Twitter. It facilitates data gathering but does not perform opinion measurement itself.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Gaussian Naive Bayes</t>
+          <t>VADER</t>
         </is>
       </c>
       <c r="B105">
-        <v>11</v>
+        <v>198</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>single_purpose_nlp</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4542,37 +4542,37 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>Gaussian Naive Bayes is a probabilistic classification algorithm that can be applied to sentiment or opinion classification tasks, but it is a general machine‑learning method rather than a tool specifically built for opinion measurement.</t>
+          <t>VADER is a rule-based sentiment analysis tool specifically designed for social media text. It uses a curated lexicon and linguistic rules to classify text into sentiment categories and output scores, but does not generate numerical text representations or identify specific opinion targets.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>HMM</t>
+          <t>WEKA</t>
         </is>
       </c>
       <c r="B106">
-        <v>11</v>
+        <v>49</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>algorithm</t>
+          <t>gui_tool</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4582,32 +4582,32 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Hidden Markov Model (HMM) is a statistical algorithm for modeling sequential data. It can be applied to opinion/sentiment analysis tasks but is not specifically designed for opinion measurement and is not provided as standalone software.</t>
+          <t>WEKA is a widely used machine learning workbench that provides a graphical user interface and command-line tools for data preprocessing, classification, regression, and clustering. It serves as a general-purpose data mining toolkit rather than a tool specifically designed for opinion measurement.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>NVivo</t>
+          <t>Word Embeddings</t>
         </is>
       </c>
       <c r="B107">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>gui_tool</t>
+          <t>approach</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -4622,37 +4622,37 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>NVivo is a commercial desktop application with a graphical user interface for qualitative data analysis. It can be used to code and explore opinionated text, but it is not a dedicated opinion‑measurement system.</t>
+          <t>Word embeddings are a conceptual approach for representing words as dense numerical vectors in a continuous space. They are specifically designed for text representation and serve as input for downstream tasks rather than being a standalone software product.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SnowNLP</t>
+          <t>WordNet</t>
         </is>
       </c>
       <c r="B108">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>general_purpose_nlp</t>
+          <t>linguistic_resource</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4662,37 +4662,37 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>SnowNLP is a Python library for Chinese text processing that provides functions for sentiment analysis, text classification, keyword extraction, etc. It can be used for opinion measurement but is not dedicated solely to that purpose.</t>
+          <t>WordNet is a comprehensive lexical database that groups English words into synonym sets and maps semantic relations. It serves as a foundational linguistic resource for NLP but does not inherently perform computational tasks like representation, classification, or target identification.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>TensorFlow</t>
+          <t>XGBoost</t>
         </is>
       </c>
       <c r="B109">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>general_library</t>
+          <t>algorithm</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -4712,47 +4712,367 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>TensorFlow is a widely‑used open‑source deep‑learning framework that can be employed to build models for opinion/sentiment analysis, though it is not specifically designed for that purpose.</t>
+          <t>XGBoost is a highly optimized gradient boosting library used for machine learning tasks like classification and regression. It is a general-purpose ML algorithm rather than a tool specifically designed for opinion measurement.</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
+          <t>XLM-RoBERTa</t>
+        </is>
+      </c>
+      <c r="B110">
+        <v>13</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>XLM-RoBERTa is a pre-trained multilingual transformer model that generates contextual text embeddings and can be fine-tuned for classification tasks like sentiment or stance analysis, but it is not specifically designed for opinion measurement or target identification out-of-the-box.</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>XLNet</t>
+        </is>
+      </c>
+      <c r="B111">
+        <v>15</v>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>model</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>XLNet is a pre-trained transformer language model that learns contextualized text representations through a permutation-based autoregressive objective. It is typically fine-tuned for downstream tasks like classification but is not specifically designed for opinion measurement or target identification.</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>doc2vec</t>
+        </is>
+      </c>
+      <c r="B112">
+        <v>22</v>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>algorithm</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Doc2vec is an algorithm for learning fixed-size vector representations of variable-length text documents. It is specifically designed for text representation, but the name refers to the methodological approach rather than a standalone installable software product.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>fastText</t>
+        </is>
+      </c>
+      <c r="B113">
+        <v>58</v>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>general_purpose_nlp</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>fastText is an open-source library developed by FAIR for efficient text representation and classification. It provides word/sentence embeddings and a supervised classifier, making it suitable for opinion measurement pipelines but not specifically designed for opinion analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>k-means</t>
+        </is>
+      </c>
+      <c r="B114">
+        <v>23</v>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>algorithm</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>K-means is a general unsupervised clustering algorithm used to partition numerical data into k groups based on similarity. It is not specifically designed for opinion measurement and does not inherently process text or identify targets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
           <t>n-gram</t>
         </is>
       </c>
-      <c r="B110">
+      <c r="B115">
         <v>11</v>
       </c>
-      <c r="C110" t="inlineStr">
+      <c r="C115" t="inlineStr">
         <is>
           <t>approach</t>
         </is>
       </c>
-      <c r="D110" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>An n‑gram is a statistical language modeling approach that captures contiguous sequences of tokens; it can be used as a feature for opinion/sentiment analysis but is not a dedicated opinion measurement tool.</t>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>N-grams are a statistical text representation technique that extracts contiguous sequences of n items from text to create feature vectors (e.g., bag-of-n-grams). They are a conceptual method rather than a standalone software product.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>scikit-learn</t>
+        </is>
+      </c>
+      <c r="B116">
+        <v>38</v>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>general_library</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>scikit-learn is a widely used open-source machine learning library for Python that provides tools for data mining and analysis, including classification, regression, and clustering algorithms. It is a general-purpose ML library rather than a tool specifically designed for opinion measurement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>spaCy</t>
+        </is>
+      </c>
+      <c r="B117">
+        <v>15</v>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>general_purpose_nlp</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>spaCy is a widely used, open-source Python library for advanced natural language processing. It provides a comprehensive pipeline for tokenization, POS tagging, named entity recognition, and word vectors, making it suitable for text representation, classification, and target identification in opinion measurement workflows.</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>word2vec</t>
+        </is>
+      </c>
+      <c r="B118">
+        <v>189</v>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>algorithm</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>word2vec is a general algorithm and model architecture for learning dense vector representations of words from text corpora. It is specifically designed for text representation but is not a standalone software product itself.</t>
         </is>
       </c>
     </row>
